--- a/Step2/Outputs/High_comparison.xlsx
+++ b/Step2/Outputs/High_comparison.xlsx
@@ -538,19 +538,19 @@
         <v>14</v>
       </c>
       <c r="C4">
-        <v>-522.5685108179823</v>
+        <v>-522.568508717497</v>
       </c>
       <c r="D4">
-        <v>16.00151747000928</v>
+        <v>16.00151730686412</v>
       </c>
       <c r="E4">
-        <v>88.99782837999737</v>
+        <v>88.997827823634</v>
       </c>
       <c r="F4">
-        <v>78.9996736299945</v>
+        <v>78.99967300005665</v>
       </c>
       <c r="G4">
-        <v>322.9906242900215</v>
+        <v>322.9906222852223</v>
       </c>
       <c r="J4">
         <v>10</v>
@@ -559,19 +559,19 @@
         <v>15</v>
       </c>
       <c r="L4">
-        <v>120.5850365220176</v>
+        <v>120.5850366449376</v>
       </c>
       <c r="M4">
-        <v>751.9562422900126</v>
+        <v>751.9562387045808</v>
       </c>
       <c r="N4">
-        <v>1498.915832070001</v>
+        <v>1498.915824763404</v>
       </c>
       <c r="O4">
-        <v>2327.868159240024</v>
+        <v>2327.868148023503</v>
       </c>
       <c r="P4">
-        <v>4189.76570202005</v>
+        <v>4189.765681501754</v>
       </c>
       <c r="S4">
         <v>10</v>
@@ -580,19 +580,19 @@
         <v>16</v>
       </c>
       <c r="U4">
-        <v>431.379184476009</v>
+        <v>431.3791822158783</v>
       </c>
       <c r="V4">
-        <v>720.9670605000028</v>
+        <v>720.9670561275852</v>
       </c>
       <c r="W4">
-        <v>1408.935951010008</v>
+        <v>1408.935942543318</v>
       </c>
       <c r="X4">
-        <v>2284.893735759979</v>
+        <v>2284.893722246175</v>
       </c>
       <c r="Y4">
-        <v>4305.796413600019</v>
+        <v>4305.796388730847</v>
       </c>
       <c r="AB4">
         <v>10</v>
@@ -601,19 +601,19 @@
         <v>17</v>
       </c>
       <c r="AD4">
-        <v>191.3942768879979</v>
+        <v>191.3942756613524</v>
       </c>
       <c r="AE4">
-        <v>211.9940841099997</v>
+        <v>211.9940826059428</v>
       </c>
       <c r="AF4">
-        <v>421.9849336600037</v>
+        <v>421.9849306772276</v>
       </c>
       <c r="AG4">
-        <v>729.9735721500019</v>
+        <v>729.9735670779482</v>
       </c>
       <c r="AH4">
-        <v>1433.945524960009</v>
+        <v>1433.945515112555</v>
       </c>
       <c r="AK4">
         <v>10</v>
@@ -622,19 +622,19 @@
         <v>11</v>
       </c>
       <c r="AM4">
-        <v>801.5890884899418</v>
+        <v>801.5890834772435</v>
       </c>
       <c r="AN4">
-        <v>819.9881339699205</v>
+        <v>819.9881288718898</v>
       </c>
       <c r="AO4">
-        <v>3189.954177429929</v>
+        <v>3189.95415759203</v>
       </c>
       <c r="AP4">
-        <v>5906.91628785996</v>
+        <v>5906.916251072835</v>
       </c>
       <c r="AQ4">
-        <v>12808.82025361998</v>
+        <v>12808.82017393154</v>
       </c>
       <c r="AT4">
         <v>10</v>
@@ -643,19 +643,19 @@
         <v>12</v>
       </c>
       <c r="AV4">
-        <v>468.581655011978</v>
+        <v>468.5816522096284</v>
       </c>
       <c r="AW4">
-        <v>727.9623706900602</v>
+        <v>727.9623661261867</v>
       </c>
       <c r="AX4">
-        <v>2765.876640950126</v>
+        <v>2765.876624221943</v>
       </c>
       <c r="AY4">
-        <v>5737.742458740002</v>
+        <v>5737.742425783246</v>
       </c>
       <c r="AZ4">
-        <v>11993.45591332001</v>
+        <v>11993.45584569147</v>
       </c>
     </row>
     <row r="5" spans="1:52">
@@ -666,19 +666,19 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>-105.1657772880008</v>
+        <v>-105.1657763839976</v>
       </c>
       <c r="D5">
-        <v>35.8069103200005</v>
+        <v>35.80690982729357</v>
       </c>
       <c r="E5">
-        <v>84.82687676000023</v>
+        <v>84.82687564993284</v>
       </c>
       <c r="F5">
-        <v>122.6231897700009</v>
+        <v>122.6231881840995</v>
       </c>
       <c r="G5">
-        <v>261.6709943900023</v>
+        <v>261.6709910429281</v>
       </c>
       <c r="J5">
         <v>2</v>
@@ -687,19 +687,19 @@
         <v>15</v>
       </c>
       <c r="L5">
-        <v>-45.72317254799782</v>
+        <v>-45.72317187375302</v>
       </c>
       <c r="M5">
-        <v>423.9558246699926</v>
+        <v>423.9558200670217</v>
       </c>
       <c r="N5">
-        <v>805.7105612400155</v>
+        <v>805.7105525057523</v>
       </c>
       <c r="O5">
-        <v>1215.292413330015</v>
+        <v>1215.292400068309</v>
       </c>
       <c r="P5">
-        <v>2170.878878569994</v>
+        <v>2170.878854708335</v>
       </c>
       <c r="S5">
         <v>2</v>
@@ -708,19 +708,19 @@
         <v>16</v>
       </c>
       <c r="U5">
-        <v>209.9330663879955</v>
+        <v>209.9330642042987</v>
       </c>
       <c r="V5">
-        <v>585.2386345800187</v>
+        <v>585.2386274754317</v>
       </c>
       <c r="W5">
-        <v>1104.442078859989</v>
+        <v>1104.442065424282</v>
       </c>
       <c r="X5">
-        <v>1711.868432640003</v>
+        <v>1711.868412040803</v>
       </c>
       <c r="Y5">
-        <v>3070.953966479985</v>
+        <v>3070.953929706124</v>
       </c>
       <c r="AB5">
         <v>2</v>
@@ -729,19 +729,19 @@
         <v>17</v>
       </c>
       <c r="AD5">
-        <v>112.3762287539939</v>
+        <v>112.376227362638</v>
       </c>
       <c r="AE5">
-        <v>167.5208603099973</v>
+        <v>167.5208580091094</v>
       </c>
       <c r="AF5">
-        <v>343.2458029600029</v>
+        <v>343.2457981740054</v>
       </c>
       <c r="AG5">
-        <v>570.1962617600038</v>
+        <v>570.1962538391799</v>
       </c>
       <c r="AH5">
-        <v>1123.781430280005</v>
+        <v>1123.78141490194</v>
       </c>
       <c r="AK5">
         <v>2</v>
@@ -750,19 +750,19 @@
         <v>11</v>
       </c>
       <c r="AM5">
-        <v>438.8981493240135</v>
+        <v>438.8981441921351</v>
       </c>
       <c r="AN5">
-        <v>440.5791337799892</v>
+        <v>440.5791286047752</v>
       </c>
       <c r="AO5">
-        <v>1730.126225089974</v>
+        <v>1730.126204771776</v>
       </c>
       <c r="AP5">
-        <v>3205.531584989993</v>
+        <v>3205.531547349325</v>
       </c>
       <c r="AQ5">
-        <v>6950.888925719992</v>
+        <v>6950.888844144603</v>
       </c>
       <c r="AT5">
         <v>2</v>
@@ -771,19 +771,19 @@
         <v>12</v>
       </c>
       <c r="AV5">
-        <v>299.5090603380231</v>
+        <v>299.509056792871</v>
       </c>
       <c r="AW5">
-        <v>766.4006916800136</v>
+        <v>766.4006823408999</v>
       </c>
       <c r="AX5">
-        <v>2194.148423829989</v>
+        <v>2194.148396653822</v>
       </c>
       <c r="AY5">
-        <v>3884.765237029991</v>
+        <v>3884.765189622281</v>
       </c>
       <c r="AZ5">
-        <v>7491.967296680043</v>
+        <v>7491.967205512818</v>
       </c>
     </row>
     <row r="6" spans="1:52">
@@ -794,19 +794,19 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>-521.2496567940034</v>
+        <v>-521.249653402585</v>
       </c>
       <c r="D6">
-        <v>-81.92336180998973</v>
+        <v>-81.92336201440412</v>
       </c>
       <c r="E6">
-        <v>-50.9127138799995</v>
+        <v>-50.9127148520347</v>
       </c>
       <c r="F6">
-        <v>-73.87948598999719</v>
+        <v>-73.87948736321414</v>
       </c>
       <c r="G6">
-        <v>163.120752730003</v>
+        <v>163.120748662539</v>
       </c>
       <c r="J6">
         <v>9</v>
@@ -815,19 +815,19 @@
         <v>15</v>
       </c>
       <c r="L6">
-        <v>119.4181003740086</v>
+        <v>119.4180985476705</v>
       </c>
       <c r="M6">
-        <v>487.8713186699897</v>
+        <v>487.8713156858576</v>
       </c>
       <c r="N6">
-        <v>1012.73137945999</v>
+        <v>1012.731373215596</v>
       </c>
       <c r="O6">
-        <v>1630.59075607</v>
+        <v>1630.59074565459</v>
       </c>
       <c r="P6">
-        <v>3042.223755240026</v>
+        <v>3042.223735905201</v>
       </c>
       <c r="S6">
         <v>9</v>
@@ -836,19 +836,19 @@
         <v>16</v>
       </c>
       <c r="U6">
-        <v>359.8705560540002</v>
+        <v>359.8705545340636</v>
       </c>
       <c r="V6">
-        <v>508.7866388799994</v>
+        <v>508.78663708776</v>
       </c>
       <c r="W6">
-        <v>1008.594631330012</v>
+        <v>1008.594627721628</v>
       </c>
       <c r="X6">
-        <v>1659.348729359997</v>
+        <v>1659.348723278345</v>
       </c>
       <c r="Y6">
-        <v>3172.792530599996</v>
+        <v>3172.792518663937</v>
       </c>
       <c r="AB6">
         <v>9</v>
@@ -857,19 +857,19 @@
         <v>17</v>
       </c>
       <c r="AD6">
-        <v>148.1423504759978</v>
+        <v>148.14234988515</v>
       </c>
       <c r="AE6">
-        <v>140.9254336000013</v>
+        <v>140.9254330258309</v>
       </c>
       <c r="AF6">
-        <v>280.8621939499981</v>
+        <v>280.8621928756966</v>
       </c>
       <c r="AG6">
-        <v>486.7558511100015</v>
+        <v>486.7558493040233</v>
       </c>
       <c r="AH6">
-        <v>962.4899588800026</v>
+        <v>962.4899554049634</v>
       </c>
       <c r="AK6">
         <v>9</v>
@@ -878,19 +878,19 @@
         <v>11</v>
       </c>
       <c r="AM6">
-        <v>770.6595463200065</v>
+        <v>770.6595402799576</v>
       </c>
       <c r="AN6">
-        <v>784.6509378599294</v>
+        <v>784.6509317418968</v>
       </c>
       <c r="AO6">
-        <v>3059.668907780084</v>
+        <v>3059.668883795501</v>
       </c>
       <c r="AP6">
-        <v>5663.534204990021</v>
+        <v>5663.534160582873</v>
       </c>
       <c r="AQ6">
-        <v>12291.65350124991</v>
+        <v>12291.65340484507</v>
       </c>
       <c r="AT6">
         <v>9</v>
@@ -899,19 +899,19 @@
         <v>12</v>
       </c>
       <c r="AV6">
-        <v>286.1297227378964</v>
+        <v>286.1297207839525</v>
       </c>
       <c r="AW6">
-        <v>130.98274243997</v>
+        <v>130.9827407582779</v>
       </c>
       <c r="AX6">
-        <v>1579.525320069923</v>
+        <v>1579.525311583478</v>
       </c>
       <c r="AY6">
-        <v>3747.79921523</v>
+        <v>3747.799196564083</v>
       </c>
       <c r="AZ6">
-        <v>8367.331795790087</v>
+        <v>8367.331753058097</v>
       </c>
     </row>
     <row r="7" spans="1:52">
@@ -922,19 +922,19 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>-26.93902858800038</v>
+        <v>-26.93902806821097</v>
       </c>
       <c r="D7">
-        <v>13.89529241000037</v>
+        <v>13.89529238390105</v>
       </c>
       <c r="E7">
-        <v>27.23868744000038</v>
+        <v>27.23868734444022</v>
       </c>
       <c r="F7">
-        <v>37.58172475000038</v>
+        <v>37.58172460743481</v>
       </c>
       <c r="G7">
-        <v>84.26831753999977</v>
+        <v>84.26831705785708</v>
       </c>
       <c r="J7">
         <v>7</v>
@@ -943,19 +943,19 @@
         <v>15</v>
       </c>
       <c r="L7">
-        <v>-19.40505676199882</v>
+        <v>-19.40505674669384</v>
       </c>
       <c r="M7">
-        <v>122.1662695600007</v>
+        <v>122.1662683757659</v>
       </c>
       <c r="N7">
-        <v>235.8844464999984</v>
+        <v>235.8844442541504</v>
       </c>
       <c r="O7">
-        <v>354.0503393700001</v>
+        <v>354.050335946089</v>
       </c>
       <c r="P7">
-        <v>646.964445409998</v>
+        <v>646.9644393082181</v>
       </c>
       <c r="S7">
         <v>7</v>
@@ -964,19 +964,19 @@
         <v>16</v>
       </c>
       <c r="U7">
-        <v>61.88175628799854</v>
+        <v>61.88175566661539</v>
       </c>
       <c r="V7">
-        <v>186.7464707699956</v>
+        <v>186.746469333917</v>
       </c>
       <c r="W7">
-        <v>350.1497100900015</v>
+        <v>350.1497073766213</v>
       </c>
       <c r="X7">
-        <v>535.4492290899998</v>
+        <v>535.4492248717243</v>
       </c>
       <c r="Y7">
-        <v>956.4963444199984</v>
+        <v>956.4963368605504</v>
       </c>
       <c r="AB7">
         <v>7</v>
@@ -985,19 +985,19 @@
         <v>17</v>
       </c>
       <c r="AD7">
-        <v>40.09221448200151</v>
+        <v>40.09221415422144</v>
       </c>
       <c r="AE7">
-        <v>61.16314753000006</v>
+        <v>61.16314707439142</v>
       </c>
       <c r="AF7">
-        <v>119.3261964099984</v>
+        <v>119.3261954982349</v>
       </c>
       <c r="AG7">
-        <v>204.7276512100002</v>
+        <v>204.7276496667728</v>
       </c>
       <c r="AH7">
-        <v>408.350510440001</v>
+        <v>408.3505073298638</v>
       </c>
       <c r="AK7">
         <v>7</v>
@@ -1006,19 +1006,19 @@
         <v>11</v>
       </c>
       <c r="AM7">
-        <v>136.7016762960047</v>
+        <v>136.7016753434727</v>
       </c>
       <c r="AN7">
-        <v>138.8807954299918</v>
+        <v>138.8807944622822</v>
       </c>
       <c r="AO7">
-        <v>542.2847701099927</v>
+        <v>542.2847663052198</v>
       </c>
       <c r="AP7">
-        <v>1002.957269429993</v>
+        <v>1002.957262456697</v>
       </c>
       <c r="AQ7">
-        <v>2173.929864939993</v>
+        <v>2173.929849743487</v>
       </c>
       <c r="AT7">
         <v>7</v>
@@ -1027,19 +1027,19 @@
         <v>12</v>
       </c>
       <c r="AV7">
-        <v>96.98517353400894</v>
+        <v>96.98517275330596</v>
       </c>
       <c r="AW7">
-        <v>188.540890150005</v>
+        <v>188.5408884947683</v>
       </c>
       <c r="AX7">
-        <v>602.3025612299934</v>
+        <v>602.3025561271133</v>
       </c>
       <c r="AY7">
-        <v>1128.573055860004</v>
+        <v>1128.573046419351</v>
       </c>
       <c r="AZ7">
-        <v>2244.276908560001</v>
+        <v>2244.276889853267</v>
       </c>
     </row>
     <row r="8" spans="1:52">
@@ -1050,19 +1050,19 @@
         <v>14</v>
       </c>
       <c r="C8">
-        <v>-101.1515665679999</v>
+        <v>-101.1515668359261</v>
       </c>
       <c r="D8">
-        <v>45.82369135999943</v>
+        <v>45.8236913540477</v>
       </c>
       <c r="E8">
-        <v>88.67959368000174</v>
+        <v>88.67959373395661</v>
       </c>
       <c r="F8">
-        <v>114.507319450001</v>
+        <v>114.5073193604458</v>
       </c>
       <c r="G8">
-        <v>229.490086869996</v>
+        <v>229.4900867370361</v>
       </c>
       <c r="J8">
         <v>8</v>
@@ -1071,19 +1071,19 @@
         <v>15</v>
       </c>
       <c r="L8">
-        <v>-28.74839994599461</v>
+        <v>-28.74839983245329</v>
       </c>
       <c r="M8">
-        <v>336.8730333000058</v>
+        <v>336.8730336132758</v>
       </c>
       <c r="N8">
-        <v>648.8781580499963</v>
+        <v>648.878158650612</v>
       </c>
       <c r="O8">
-        <v>982.4084305699872</v>
+        <v>982.4084317501693</v>
       </c>
       <c r="P8">
-        <v>1738.752430319993</v>
+        <v>1738.752432074987</v>
       </c>
       <c r="S8">
         <v>8</v>
@@ -1092,19 +1092,19 @@
         <v>16</v>
       </c>
       <c r="U8">
-        <v>144.3580645500006</v>
+        <v>144.358064756605</v>
       </c>
       <c r="V8">
-        <v>431.8182067999915</v>
+        <v>431.8182069365757</v>
       </c>
       <c r="W8">
-        <v>821.4782750799968</v>
+        <v>821.4782752920873</v>
       </c>
       <c r="X8">
-        <v>1257.273287360007</v>
+        <v>1257.273287864637</v>
       </c>
       <c r="Y8">
-        <v>2197.767917339996</v>
+        <v>2197.767918280239</v>
       </c>
       <c r="AB8">
         <v>8</v>
@@ -1113,19 +1113,19 @@
         <v>17</v>
       </c>
       <c r="AD8">
-        <v>99.09122826600468</v>
+        <v>99.09122825744272</v>
       </c>
       <c r="AE8">
-        <v>169.5708950999961</v>
+        <v>169.5708950082435</v>
       </c>
       <c r="AF8">
-        <v>353.1483503199988</v>
+        <v>353.1483500759332</v>
       </c>
       <c r="AG8">
-        <v>588.9918177199925</v>
+        <v>588.9918170603378</v>
       </c>
       <c r="AH8">
-        <v>1138.181212149995</v>
+        <v>1138.181211215483</v>
       </c>
       <c r="AK8">
         <v>8</v>
@@ -1134,19 +1134,19 @@
         <v>11</v>
       </c>
       <c r="AM8">
-        <v>479.9677190639341</v>
+        <v>479.9677181102888</v>
       </c>
       <c r="AN8">
-        <v>492.7435849100148</v>
+        <v>492.7435839596728</v>
       </c>
       <c r="AO8">
-        <v>1915.649980219983</v>
+        <v>1915.649976615896</v>
       </c>
       <c r="AP8">
-        <v>3542.134002040038</v>
+        <v>3542.133995262193</v>
       </c>
       <c r="AQ8">
-        <v>7690.266159269973</v>
+        <v>7690.266144651832</v>
       </c>
       <c r="AT8">
         <v>8</v>
@@ -1155,19 +1155,19 @@
         <v>12</v>
       </c>
       <c r="AV8">
-        <v>216.9679968059864</v>
+        <v>216.9679969756617</v>
       </c>
       <c r="AW8">
-        <v>629.8079069699743</v>
+        <v>629.807906873415</v>
       </c>
       <c r="AX8">
-        <v>1793.627061130006</v>
+        <v>1793.627061300824</v>
       </c>
       <c r="AY8">
-        <v>3141.521768029997</v>
+        <v>3141.521766829333</v>
       </c>
       <c r="AZ8">
-        <v>5946.244734869986</v>
+        <v>5946.244734373664</v>
       </c>
     </row>
     <row r="9" spans="1:52">
@@ -1178,19 +1178,19 @@
         <v>14</v>
       </c>
       <c r="C9">
-        <v>-194.9783925479933</v>
+        <v>-194.9783927717999</v>
       </c>
       <c r="D9">
-        <v>-4.998740780007211</v>
+        <v>-4.998740857334269</v>
       </c>
       <c r="E9">
-        <v>12.00066269000126</v>
+        <v>12.00066259692358</v>
       </c>
       <c r="F9">
-        <v>7.00124565999613</v>
+        <v>7.001245525903869</v>
       </c>
       <c r="G9">
-        <v>107.9899311300014</v>
+        <v>107.9899310103574</v>
       </c>
       <c r="J9">
         <v>5</v>
@@ -1199,19 +1199,19 @@
         <v>15</v>
       </c>
       <c r="L9">
-        <v>-10.7983359300124</v>
+        <v>-10.79833600646089</v>
       </c>
       <c r="M9">
-        <v>351.9651498999883</v>
+        <v>351.9651502020024</v>
       </c>
       <c r="N9">
-        <v>688.9326015400002</v>
+        <v>688.932602150242</v>
       </c>
       <c r="O9">
-        <v>1066.896177499999</v>
+        <v>1066.896178438954</v>
       </c>
       <c r="P9">
-        <v>1943.807987969994</v>
+        <v>1943.807989700756</v>
       </c>
       <c r="S9">
         <v>5</v>
@@ -1220,19 +1220,19 @@
         <v>16</v>
       </c>
       <c r="U9">
-        <v>196.178997192008</v>
+        <v>196.1789974105504</v>
       </c>
       <c r="V9">
-        <v>425.9581664699981</v>
+        <v>425.9581669689978</v>
       </c>
       <c r="W9">
-        <v>831.9170551000007</v>
+        <v>831.9170560929306</v>
       </c>
       <c r="X9">
-        <v>1321.866969339997</v>
+        <v>1321.866970882391</v>
       </c>
       <c r="Y9">
-        <v>2445.749066209999</v>
+        <v>2445.74906898808</v>
       </c>
       <c r="AB9">
         <v>5</v>
@@ -1241,19 +1241,19 @@
         <v>17</v>
       </c>
       <c r="AD9">
-        <v>104.3894515380025</v>
+        <v>104.3894516733198</v>
       </c>
       <c r="AE9">
-        <v>128.9891112400028</v>
+        <v>128.9891113973536</v>
       </c>
       <c r="AF9">
-        <v>267.9763453799987</v>
+        <v>267.9763457221852</v>
       </c>
       <c r="AG9">
-        <v>461.958357200002</v>
+        <v>461.9583578174042</v>
       </c>
       <c r="AH9">
-        <v>914.9199600800011</v>
+        <v>914.9199612938056</v>
       </c>
       <c r="AK9">
         <v>5</v>
@@ -1262,19 +1262,19 @@
         <v>11</v>
       </c>
       <c r="AM9">
-        <v>329.9670531120064</v>
+        <v>329.9670541182422</v>
       </c>
       <c r="AN9">
-        <v>334.9664873199872</v>
+        <v>334.9664883363948</v>
       </c>
       <c r="AO9">
-        <v>1306.869426829995</v>
+        <v>1306.869430804771</v>
       </c>
       <c r="AP9">
-        <v>2418.756970909977</v>
+        <v>2418.756978301993</v>
       </c>
       <c r="AQ9">
-        <v>5245.473287560017</v>
+        <v>5245.473303576189</v>
       </c>
       <c r="AT9">
         <v>5</v>
@@ -1283,19 +1283,19 @@
         <v>12</v>
       </c>
       <c r="AV9">
-        <v>193.1811760920027</v>
+        <v>193.1811762290963</v>
       </c>
       <c r="AW9">
-        <v>418.9645241499602</v>
+        <v>418.9645244863787</v>
       </c>
       <c r="AX9">
-        <v>1471.863836429991</v>
+        <v>1471.863838090401</v>
       </c>
       <c r="AY9">
-        <v>2882.714002229986</v>
+        <v>2882.714005432259</v>
       </c>
       <c r="AZ9">
-        <v>5821.422895409996</v>
+        <v>5821.422901885788</v>
       </c>
     </row>
     <row r="10" spans="1:52">
@@ -1306,19 +1306,19 @@
         <v>14</v>
       </c>
       <c r="C10">
-        <v>-109.95199314</v>
+        <v>-109.9519926607136</v>
       </c>
       <c r="D10">
-        <v>11.92384983999546</v>
+        <v>11.92384981638134</v>
       </c>
       <c r="E10">
-        <v>38.91340419999869</v>
+        <v>38.91340410883549</v>
       </c>
       <c r="F10">
-        <v>65.88068525999915</v>
+        <v>65.88068509199184</v>
       </c>
       <c r="G10">
-        <v>175.8815691999989</v>
+        <v>175.8815685797817</v>
       </c>
       <c r="J10">
         <v>3</v>
@@ -1327,19 +1327,19 @@
         <v>15</v>
       </c>
       <c r="L10">
-        <v>-70.21680813000421</v>
+        <v>-70.21680772058244</v>
       </c>
       <c r="M10">
-        <v>279.1373342199949</v>
+        <v>279.1373330619463</v>
       </c>
       <c r="N10">
-        <v>558.2855888800004</v>
+        <v>558.2855866011923</v>
       </c>
       <c r="O10">
-        <v>855.4323375199965</v>
+        <v>855.4323340804003</v>
       </c>
       <c r="P10">
-        <v>1574.814022769995</v>
+        <v>1574.814016300388</v>
       </c>
       <c r="S10">
         <v>3</v>
@@ -1348,19 +1348,19 @@
         <v>16</v>
       </c>
       <c r="U10">
-        <v>160.3338280680036</v>
+        <v>160.3338273466397</v>
       </c>
       <c r="V10">
-        <v>437.2198566699954</v>
+        <v>437.2198545834581</v>
       </c>
       <c r="W10">
-        <v>844.4179544300096</v>
+        <v>844.4179503943051</v>
       </c>
       <c r="X10">
-        <v>1314.67035036999</v>
+        <v>1314.670344098195</v>
       </c>
       <c r="Y10">
-        <v>2371.243291390001</v>
+        <v>2371.243280210692</v>
       </c>
       <c r="AB10">
         <v>3</v>
@@ -1369,19 +1369,19 @@
         <v>17</v>
       </c>
       <c r="AD10">
-        <v>97.8580954079971</v>
+        <v>97.85809494120804</v>
       </c>
       <c r="AE10">
-        <v>130.0760384499999</v>
+        <v>130.0760377855331</v>
       </c>
       <c r="AF10">
-        <v>282.1391370699939</v>
+        <v>282.1391356400736</v>
       </c>
       <c r="AG10">
-        <v>476.2473975299981</v>
+        <v>476.2473950603644</v>
       </c>
       <c r="AH10">
-        <v>927.5170396299992</v>
+        <v>927.5170346571576</v>
       </c>
       <c r="AK10">
         <v>3</v>
@@ -1390,19 +1390,19 @@
         <v>11</v>
       </c>
       <c r="AM10">
-        <v>359.7429007620158</v>
+        <v>359.7428990506742</v>
       </c>
       <c r="AN10">
-        <v>364.352038439989</v>
+        <v>364.3520366743032</v>
       </c>
       <c r="AO10">
-        <v>1426.341509209946</v>
+        <v>1426.341502367351</v>
       </c>
       <c r="AP10">
-        <v>2642.484626690006</v>
+        <v>2642.484613992143</v>
       </c>
       <c r="AQ10">
-        <v>5732.387202949984</v>
+        <v>5732.387175408709</v>
       </c>
       <c r="AT10">
         <v>3</v>
@@ -1411,19 +1411,19 @@
         <v>12</v>
       </c>
       <c r="AV10">
-        <v>165.676449797953</v>
+        <v>165.6764490600544</v>
       </c>
       <c r="AW10">
-        <v>386.0343302499969</v>
+        <v>386.0343287422365</v>
       </c>
       <c r="AX10">
-        <v>1473.50348378002</v>
+        <v>1473.503477411032</v>
       </c>
       <c r="AY10">
-        <v>2807.252164040001</v>
+        <v>2807.252150889268</v>
       </c>
       <c r="AZ10">
-        <v>5487.765924429994</v>
+        <v>5487.765898847771</v>
       </c>
     </row>
     <row r="11" spans="1:52">
@@ -1434,19 +1434,19 @@
         <v>14</v>
       </c>
       <c r="C11">
-        <v>-66.94422058800137</v>
+        <v>-66.94422059959879</v>
       </c>
       <c r="D11">
-        <v>-5.713120359999721</v>
+        <v>-5.713120395041642</v>
       </c>
       <c r="E11">
-        <v>2.573752339998919</v>
+        <v>2.57375233078983</v>
       </c>
       <c r="F11">
-        <v>3.147504799999751</v>
+        <v>3.147504785988985</v>
       </c>
       <c r="G11">
-        <v>52.58185975999959</v>
+        <v>52.58185972986848</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1455,19 +1455,19 @@
         <v>15</v>
       </c>
       <c r="L11">
-        <v>-52.63271536800312</v>
+        <v>-52.6327152789072</v>
       </c>
       <c r="M11">
-        <v>127.0080721399972</v>
+        <v>127.0080721312843</v>
       </c>
       <c r="N11">
-        <v>256.016140720003</v>
+        <v>256.0161407777814</v>
       </c>
       <c r="O11">
-        <v>392.8848366699949</v>
+        <v>392.8848367741757</v>
       </c>
       <c r="P11">
-        <v>746.482811140002</v>
+        <v>746.4828112971209</v>
       </c>
       <c r="S11">
         <v>6</v>
@@ -1476,19 +1476,19 @@
         <v>16</v>
       </c>
       <c r="U11">
-        <v>99.2605732380016</v>
+        <v>99.26057318100356</v>
       </c>
       <c r="V11">
-        <v>220.303018190003</v>
+        <v>220.3030181541817</v>
       </c>
       <c r="W11">
-        <v>430.3191654599996</v>
+        <v>430.3191653300437</v>
       </c>
       <c r="X11">
-        <v>677.6221638999996</v>
+        <v>677.6221636724531</v>
       </c>
       <c r="Y11">
-        <v>1242.236261030001</v>
+        <v>1242.236260628843</v>
       </c>
       <c r="AB11">
         <v>6</v>
@@ -1497,19 +1497,19 @@
         <v>17</v>
       </c>
       <c r="AD11">
-        <v>58.37697356400031</v>
+        <v>58.3769735441856</v>
       </c>
       <c r="AE11">
-        <v>67.58184959999926</v>
+        <v>67.58184959368009</v>
       </c>
       <c r="AF11">
-        <v>150.1636914999999</v>
+        <v>150.1636914526061</v>
       </c>
       <c r="AG11">
-        <v>263.3192676400004</v>
+        <v>263.3192674814072</v>
       </c>
       <c r="AH11">
-        <v>516.6385429499996</v>
+        <v>516.6385426637216</v>
       </c>
       <c r="AK11">
         <v>6</v>
@@ -1518,19 +1518,19 @@
         <v>11</v>
       </c>
       <c r="AM11">
-        <v>198.0291729180172</v>
+        <v>198.0291733888589</v>
       </c>
       <c r="AN11">
-        <v>204.4586703200039</v>
+        <v>204.4586708098795</v>
       </c>
       <c r="AO11">
-        <v>784.9740680900068</v>
+        <v>784.9740700072216</v>
       </c>
       <c r="AP11">
-        <v>1455.645056310001</v>
+        <v>1455.645059833507</v>
       </c>
       <c r="AQ11">
-        <v>3156.756891879995</v>
+        <v>3156.756899495748</v>
       </c>
       <c r="AT11">
         <v>6</v>
@@ -1539,19 +1539,19 @@
         <v>12</v>
       </c>
       <c r="AV11">
-        <v>88.8933365940029</v>
+        <v>88.89333659442491</v>
       </c>
       <c r="AW11">
-        <v>96.72122273999412</v>
+        <v>96.72122280334588</v>
       </c>
       <c r="AX11">
-        <v>632.6222214599984</v>
+        <v>632.6222212766006</v>
       </c>
       <c r="AY11">
-        <v>1298.244391820001</v>
+        <v>1298.244391437824</v>
       </c>
       <c r="AZ11">
-        <v>2676.652524379999</v>
+        <v>2676.652523702985</v>
       </c>
     </row>
     <row r="12" spans="1:52">
@@ -1562,19 +1562,19 @@
         <v>14</v>
       </c>
       <c r="C12">
-        <v>-154.8022486739974</v>
+        <v>-154.8022489614787</v>
       </c>
       <c r="D12">
-        <v>-42.00009432999832</v>
+        <v>-42.00009440668691</v>
       </c>
       <c r="E12">
-        <v>-51.00017925999782</v>
+        <v>-51.00017932153696</v>
       </c>
       <c r="F12">
-        <v>-73.99987568999859</v>
+        <v>-73.99987581021105</v>
       </c>
       <c r="G12">
-        <v>-27.99914055000227</v>
+        <v>-27.99914066783094</v>
       </c>
       <c r="J12">
         <v>4</v>
@@ -1583,19 +1583,19 @@
         <v>15</v>
       </c>
       <c r="L12">
-        <v>-14.39894169000399</v>
+        <v>-14.39894161610209</v>
       </c>
       <c r="M12">
-        <v>171.0041537900033</v>
+        <v>171.0041539856138</v>
       </c>
       <c r="N12">
-        <v>353.0082077799962</v>
+        <v>353.0082082081317</v>
       </c>
       <c r="O12">
-        <v>557.0131913899968</v>
+        <v>557.013192047576</v>
       </c>
       <c r="P12">
-        <v>1046.023088460006</v>
+        <v>1046.023089616938</v>
       </c>
       <c r="S12">
         <v>4</v>
@@ -1604,19 +1604,19 @@
         <v>16</v>
       </c>
       <c r="U12">
-        <v>147.0010841039966</v>
+        <v>147.0010843155669</v>
       </c>
       <c r="V12">
-        <v>236.0035375299976</v>
+        <v>236.0035376227133</v>
       </c>
       <c r="W12">
-        <v>458.0063136099961</v>
+        <v>458.0063138362784</v>
       </c>
       <c r="X12">
-        <v>734.0098639100015</v>
+        <v>734.009864264568</v>
       </c>
       <c r="Y12">
-        <v>1369.017442439999</v>
+        <v>1369.017443252293</v>
       </c>
       <c r="AB12">
         <v>4</v>
@@ -1625,19 +1625,19 @@
         <v>17</v>
       </c>
       <c r="AD12">
-        <v>62.40116270399994</v>
+        <v>62.40116273172725</v>
       </c>
       <c r="AE12">
-        <v>60.0020099999997</v>
+        <v>60.00200998730679</v>
       </c>
       <c r="AF12">
-        <v>127.0040732399984</v>
+        <v>127.0040732345219</v>
       </c>
       <c r="AG12">
-        <v>217.0065207100001</v>
+        <v>217.0065207022476</v>
       </c>
       <c r="AH12">
-        <v>418.0118921900003</v>
+        <v>418.0118921488047</v>
       </c>
       <c r="AK12">
         <v>4</v>
@@ -1646,19 +1646,19 @@
         <v>11</v>
       </c>
       <c r="AM12">
-        <v>188.410196459994</v>
+        <v>188.4101963029861</v>
       </c>
       <c r="AN12">
-        <v>189.01041575001</v>
+        <v>189.0104155928712</v>
       </c>
       <c r="AO12">
-        <v>744.0406340499903</v>
+        <v>744.0406333820865</v>
       </c>
       <c r="AP12">
-        <v>1377.075570150002</v>
+        <v>1377.075568906046</v>
       </c>
       <c r="AQ12">
-        <v>2988.163970969996</v>
+        <v>2988.163968285051</v>
       </c>
       <c r="AT12">
         <v>4</v>
@@ -1667,19 +1667,19 @@
         <v>12</v>
       </c>
       <c r="AV12">
-        <v>107.4018109740064</v>
+        <v>107.4018110546022</v>
       </c>
       <c r="AW12">
-        <v>49.00610140001663</v>
+        <v>49.0061013973027</v>
       </c>
       <c r="AX12">
-        <v>615.0168276399927</v>
+        <v>615.0168281003425</v>
       </c>
       <c r="AY12">
-        <v>1397.02713691003</v>
+        <v>1397.02713834028</v>
       </c>
       <c r="AZ12">
-        <v>3007.052485499982</v>
+        <v>3007.052488168883</v>
       </c>
     </row>
     <row r="13" spans="1:52">
@@ -1690,19 +1690,19 @@
         <v>14</v>
       </c>
       <c r="C13">
-        <v>-6.501462515999947</v>
+        <v>-6.501462455912588</v>
       </c>
       <c r="D13">
-        <v>4.965013779999822</v>
+        <v>4.965013744364114</v>
       </c>
       <c r="E13">
-        <v>10.89609770999994</v>
+        <v>10.89609763635122</v>
       </c>
       <c r="F13">
-        <v>17.86122328999988</v>
+        <v>17.86122317017794</v>
       </c>
       <c r="G13">
-        <v>39.65615496000009</v>
+        <v>39.65615465878364</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1711,19 +1711,19 @@
         <v>15</v>
       </c>
       <c r="L13">
-        <v>-11.91735815399988</v>
+        <v>-11.91735800733113</v>
       </c>
       <c r="M13">
-        <v>46.48816784000019</v>
+        <v>46.4881674557646</v>
       </c>
       <c r="N13">
-        <v>88.04483093999988</v>
+        <v>88.04483021031047</v>
       </c>
       <c r="O13">
-        <v>138.4646187999992</v>
+        <v>138.464617659095</v>
       </c>
       <c r="P13">
-        <v>251.23705814</v>
+        <v>251.2370561158027</v>
       </c>
       <c r="S13">
         <v>1</v>
@@ -1732,19 +1732,19 @@
         <v>16</v>
       </c>
       <c r="U13">
-        <v>23.75541850800028</v>
+        <v>23.75541826315793</v>
       </c>
       <c r="V13">
-        <v>85.10746883000047</v>
+        <v>85.10746808248678</v>
       </c>
       <c r="W13">
-        <v>155.3894197900003</v>
+        <v>155.3894184386759</v>
       </c>
       <c r="X13">
-        <v>235.53415275</v>
+        <v>235.5341506755194</v>
       </c>
       <c r="Y13">
-        <v>412.7259272599986</v>
+        <v>412.7259236452905</v>
       </c>
       <c r="AB13">
         <v>1</v>
@@ -1753,19 +1753,19 @@
         <v>17</v>
       </c>
       <c r="AD13">
-        <v>21.37308295799994</v>
+        <v>21.37308275851001</v>
       </c>
       <c r="AE13">
-        <v>36.58505312999978</v>
+        <v>36.58505283332556</v>
       </c>
       <c r="AF13">
-        <v>73.17094683999994</v>
+        <v>73.17094627229608</v>
       </c>
       <c r="AG13">
-        <v>117.68762182</v>
+        <v>117.6876209013226</v>
       </c>
       <c r="AH13">
-        <v>236.3747035299996</v>
+        <v>236.3747016679133</v>
       </c>
       <c r="AK13">
         <v>1</v>
@@ -1774,19 +1774,19 @@
         <v>11</v>
       </c>
       <c r="AM13">
-        <v>37.40686720200029</v>
+        <v>37.40686687089783</v>
       </c>
       <c r="AN13">
-        <v>38.58594709999943</v>
+        <v>38.58594675759741</v>
       </c>
       <c r="AO13">
-        <v>149.4834748200001</v>
+        <v>149.4834734924771</v>
       </c>
       <c r="AP13">
-        <v>278.1738725199993</v>
+        <v>278.1738700389751</v>
       </c>
       <c r="AQ13">
-        <v>603.8652072200002</v>
+        <v>603.8652018351804</v>
       </c>
       <c r="AT13">
         <v>1</v>
@@ -1795,19 +1795,19 @@
         <v>12</v>
       </c>
       <c r="AV13">
-        <v>46.883206986</v>
+        <v>46.88320659301644</v>
       </c>
       <c r="AW13">
-        <v>94.07266188000358</v>
+        <v>94.07266105735836</v>
       </c>
       <c r="AX13">
-        <v>280.0530421000003</v>
+        <v>280.0530398505034</v>
       </c>
       <c r="AY13">
-        <v>483.0787011899975</v>
+        <v>483.0786973684208</v>
       </c>
       <c r="AZ13">
-        <v>987.737329069996</v>
+        <v>987.7373210346832</v>
       </c>
     </row>
     <row r="14" spans="1:52">
@@ -1818,19 +1818,19 @@
         <v>14</v>
       </c>
       <c r="C14">
-        <v>-258.0000016139911</v>
+        <v>-258.0000000433174</v>
       </c>
       <c r="D14">
-        <v>-54.00000025000736</v>
+        <v>-54.00000000096225</v>
       </c>
       <c r="E14">
-        <v>-68.00000031999116</v>
+        <v>-67.9999999979118</v>
       </c>
       <c r="F14">
-        <v>-112.0000005999936</v>
+        <v>-111.9999999998909</v>
       </c>
       <c r="G14">
-        <v>-70.0000004400099</v>
+        <v>-69.99999998878047</v>
       </c>
       <c r="J14">
         <v>17</v>
@@ -1839,19 +1839,19 @@
         <v>15</v>
       </c>
       <c r="L14">
-        <v>-6.59999969999626</v>
+        <v>-6.599999979192944</v>
       </c>
       <c r="M14">
-        <v>383.000002179997</v>
+        <v>383.0000000624823</v>
       </c>
       <c r="N14">
-        <v>744.0000042399988</v>
+        <v>744.0000001217704</v>
       </c>
       <c r="O14">
-        <v>1127.000006449976</v>
+        <v>1127.000000189732</v>
       </c>
       <c r="P14">
-        <v>2040.00001158</v>
+        <v>2040.000000351167</v>
       </c>
       <c r="S14">
         <v>17</v>
@@ -1860,19 +1860,19 @@
         <v>16</v>
       </c>
       <c r="U14">
-        <v>226.2000011700001</v>
+        <v>226.2000000256212</v>
       </c>
       <c r="V14">
-        <v>418.0000019100062</v>
+        <v>418.0000000369782</v>
       </c>
       <c r="W14">
-        <v>812.0000038399976</v>
+        <v>812.0000000733817</v>
       </c>
       <c r="X14">
-        <v>1281.000006189988</v>
+        <v>1281.000000120504</v>
       </c>
       <c r="Y14">
-        <v>2338.000011500008</v>
+        <v>2338.000000226726</v>
       </c>
       <c r="AB14">
         <v>17</v>
@@ -1881,19 +1881,19 @@
         <v>17</v>
       </c>
       <c r="AD14">
-        <v>123.0000005520005</v>
+        <v>123.0000000081191</v>
       </c>
       <c r="AE14">
-        <v>157.0000006499986</v>
+        <v>157.0000000062755</v>
       </c>
       <c r="AF14">
-        <v>334.0000013099998</v>
+        <v>334.0000000101918</v>
       </c>
       <c r="AG14">
-        <v>581.0000023100001</v>
+        <v>581.0000000179307</v>
       </c>
       <c r="AH14">
-        <v>1124.000004540003</v>
+        <v>1124.000000034461</v>
       </c>
       <c r="AK14">
         <v>17</v>
@@ -1902,19 +1902,19 @@
         <v>11</v>
       </c>
       <c r="AM14">
-        <v>400.2000023699802</v>
+        <v>400.2000000599655</v>
       </c>
       <c r="AN14">
-        <v>411.0000024799956</v>
+        <v>411.0000000610889</v>
       </c>
       <c r="AO14">
-        <v>1597.00000953002</v>
+        <v>1597.000000242828</v>
       </c>
       <c r="AP14">
-        <v>2954.000017640036</v>
+        <v>2954.000000451095</v>
       </c>
       <c r="AQ14">
-        <v>6404.000038229977</v>
+        <v>6404.000000978835</v>
       </c>
       <c r="AT14">
         <v>17</v>
@@ -1923,19 +1923,19 @@
         <v>12</v>
       </c>
       <c r="AV14">
-        <v>194.4000009419906</v>
+        <v>194.4000000198357</v>
       </c>
       <c r="AW14">
-        <v>352.0000017199418</v>
+        <v>352.0000000360378</v>
       </c>
       <c r="AX14">
-        <v>1417.000007110015</v>
+        <v>1417.000000149863</v>
       </c>
       <c r="AY14">
-        <v>2822.000014409998</v>
+        <v>2822.000000308821</v>
       </c>
       <c r="AZ14">
-        <v>5600.000028200011</v>
+        <v>5600.0000005822</v>
       </c>
     </row>
     <row r="15" spans="1:52">
@@ -1946,19 +1946,19 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>-130.9259106599984</v>
+        <v>-130.9259105793881</v>
       </c>
       <c r="D15">
-        <v>38.35665127000175</v>
+        <v>38.35665125799551</v>
       </c>
       <c r="E15">
-        <v>81.06994650999877</v>
+        <v>81.06994648067939</v>
       </c>
       <c r="F15">
-        <v>101.4265911399998</v>
+        <v>101.426591112072</v>
       </c>
       <c r="G15">
-        <v>197.5664734199981</v>
+        <v>197.56647335449</v>
       </c>
       <c r="J15">
         <v>15</v>
@@ -1967,19 +1967,19 @@
         <v>15</v>
       </c>
       <c r="L15">
-        <v>-2.697899232000054</v>
+        <v>-2.697899296017567</v>
       </c>
       <c r="M15">
-        <v>325.7763036400029</v>
+        <v>325.7763035594653</v>
       </c>
       <c r="N15">
-        <v>630.839311089996</v>
+        <v>630.8393109356803</v>
       </c>
       <c r="O15">
-        <v>945.9023255399989</v>
+        <v>945.9023252856859</v>
       </c>
       <c r="P15">
-        <v>1670.881534160006</v>
+        <v>1670.881533646003</v>
       </c>
       <c r="S15">
         <v>15</v>
@@ -1988,19 +1988,19 @@
         <v>16</v>
       </c>
       <c r="U15">
-        <v>138.5958364739981</v>
+        <v>138.5958364513644</v>
       </c>
       <c r="V15">
-        <v>351.2728044899995</v>
+        <v>351.2728044603937</v>
       </c>
       <c r="W15">
-        <v>677.7623745399978</v>
+        <v>677.7623745124347</v>
       </c>
       <c r="X15">
-        <v>1054.035184960001</v>
+        <v>1054.035184903132</v>
       </c>
       <c r="Y15">
-        <v>1911.29409086</v>
+        <v>1911.294090783158</v>
       </c>
       <c r="AB15">
         <v>15</v>
@@ -2009,19 +2009,19 @@
         <v>17</v>
       </c>
       <c r="AD15">
-        <v>75.16785658200024</v>
+        <v>75.16785656066622</v>
       </c>
       <c r="AE15">
-        <v>115.9231082000006</v>
+        <v>115.9231081736352</v>
       </c>
       <c r="AF15">
-        <v>236.5595091000005</v>
+        <v>236.5595090621646</v>
       </c>
       <c r="AG15">
-        <v>405.2658453499998</v>
+        <v>405.2658453001896</v>
       </c>
       <c r="AH15">
-        <v>760.7484566699995</v>
+        <v>760.748456610062</v>
       </c>
       <c r="AK15">
         <v>15</v>
@@ -2030,19 +2030,19 @@
         <v>11</v>
       </c>
       <c r="AM15">
-        <v>193.4476525439968</v>
+        <v>193.4476523794292</v>
       </c>
       <c r="AN15">
-        <v>195.7763224399969</v>
+        <v>195.7763222763024</v>
       </c>
       <c r="AO15">
-        <v>767.1052893899978</v>
+        <v>767.1052887532205</v>
       </c>
       <c r="AP15">
-        <v>1420.287446640003</v>
+        <v>1420.287445451795</v>
       </c>
       <c r="AQ15">
-        <v>3080.134459009991</v>
+        <v>3080.134456420616</v>
       </c>
       <c r="AT15">
         <v>15</v>
@@ -2051,19 +2051,19 @@
         <v>12</v>
       </c>
       <c r="AV15">
-        <v>229.9636975859976</v>
+        <v>229.9636975225876</v>
       </c>
       <c r="AW15">
-        <v>532.7693184000018</v>
+        <v>532.7693184318268</v>
       </c>
       <c r="AX15">
-        <v>1399.238066139995</v>
+        <v>1399.238066041631</v>
       </c>
       <c r="AY15">
-        <v>2514.490030289991</v>
+        <v>2514.490030111207</v>
       </c>
       <c r="AZ15">
-        <v>4685.847141350001</v>
+        <v>4685.847140940226</v>
       </c>
     </row>
     <row r="16" spans="1:52">
@@ -2074,19 +2074,19 @@
         <v>14</v>
       </c>
       <c r="C16">
-        <v>-132.2870261040007</v>
+        <v>-132.2870255703483</v>
       </c>
       <c r="D16">
-        <v>15.79284764000022</v>
+        <v>15.79284759073107</v>
       </c>
       <c r="E16">
-        <v>33.79285657000128</v>
+        <v>33.79285650289421</v>
       </c>
       <c r="F16">
-        <v>33.0000217099996</v>
+        <v>33.00002168986794</v>
       </c>
       <c r="G16">
-        <v>114.9642654799991</v>
+        <v>114.9642652711427</v>
       </c>
       <c r="J16">
         <v>16</v>
@@ -2095,19 +2095,19 @@
         <v>15</v>
       </c>
       <c r="L16">
-        <v>-12.82713111600242</v>
+        <v>-12.82713117279127</v>
       </c>
       <c r="M16">
-        <v>311.0283202600003</v>
+        <v>311.0283192125207</v>
       </c>
       <c r="N16">
-        <v>588.4709547400016</v>
+        <v>588.4709528005005</v>
       </c>
       <c r="O16">
-        <v>884.499276999999</v>
+        <v>884.4992740716225</v>
       </c>
       <c r="P16">
-        <v>1581.313012170002</v>
+        <v>1581.313007033561</v>
       </c>
       <c r="S16">
         <v>16</v>
@@ -2116,19 +2116,19 @@
         <v>16</v>
       </c>
       <c r="U16">
-        <v>149.4384539279981</v>
+        <v>149.4384533854409</v>
       </c>
       <c r="V16">
-        <v>356.9925696099981</v>
+        <v>356.9925686457027</v>
       </c>
       <c r="W16">
-        <v>681.8137561200001</v>
+        <v>681.8137542728509</v>
       </c>
       <c r="X16">
-        <v>1054.806328160002</v>
+        <v>1054.806325225622</v>
       </c>
       <c r="Y16">
-        <v>1883.962884320002</v>
+        <v>1883.962879058967</v>
       </c>
       <c r="AB16">
         <v>16</v>
@@ -2137,19 +2137,19 @@
         <v>17</v>
       </c>
       <c r="AD16">
-        <v>94.38419882400012</v>
+        <v>94.38419858641828</v>
       </c>
       <c r="AE16">
-        <v>134.5141546699997</v>
+        <v>134.5141544148364</v>
       </c>
       <c r="AF16">
-        <v>287.8211525000006</v>
+        <v>287.8211519691531</v>
       </c>
       <c r="AG16">
-        <v>488.2995382200006</v>
+        <v>488.299537308134</v>
       </c>
       <c r="AH16">
-        <v>940.8062262999993</v>
+        <v>940.8062245274514</v>
       </c>
       <c r="AK16">
         <v>16</v>
@@ -2158,19 +2158,19 @@
         <v>11</v>
       </c>
       <c r="AM16">
-        <v>384.3254501640113</v>
+        <v>384.3254483965575</v>
       </c>
       <c r="AN16">
-        <v>388.6497469400056</v>
+        <v>388.6497451697069</v>
       </c>
       <c r="AO16">
-        <v>1524.598979660004</v>
+        <v>1524.598972678185</v>
       </c>
       <c r="AP16">
-        <v>2818.890974299997</v>
+        <v>2818.890961371115</v>
       </c>
       <c r="AQ16">
-        <v>6120.188761939993</v>
+        <v>6120.188733902702</v>
       </c>
       <c r="AT16">
         <v>16</v>
@@ -2179,19 +2179,19 @@
         <v>12</v>
       </c>
       <c r="AV16">
-        <v>272.7254691420021</v>
+        <v>272.7254682269559</v>
       </c>
       <c r="AW16">
-        <v>399.4427121199988</v>
+        <v>399.4427111262921</v>
       </c>
       <c r="AX16">
-        <v>1279.69904254999</v>
+        <v>1279.699039118881</v>
       </c>
       <c r="AY16">
-        <v>2373.091035960002</v>
+        <v>2373.091029839889</v>
       </c>
       <c r="AZ16">
-        <v>4514.360949609996</v>
+        <v>4514.360937986552</v>
       </c>
     </row>
     <row r="17" spans="1:52">
@@ -2202,19 +2202,19 @@
         <v>14</v>
       </c>
       <c r="C17">
-        <v>-26.99999402399999</v>
+        <v>-26.99999404567984</v>
       </c>
       <c r="D17">
-        <v>8.013074679999818</v>
+        <v>8.013074700145808</v>
       </c>
       <c r="E17">
-        <v>15.62353467000003</v>
+        <v>15.6235346924841</v>
       </c>
       <c r="F17">
-        <v>23.23399503999985</v>
+        <v>23.23399504847839</v>
       </c>
       <c r="G17">
-        <v>52.66275783000015</v>
+        <v>52.6627578468615</v>
       </c>
       <c r="J17">
         <v>11</v>
@@ -2223,19 +2223,19 @@
         <v>15</v>
       </c>
       <c r="L17">
-        <v>-8.407844819999809</v>
+        <v>-8.407844781913809</v>
       </c>
       <c r="M17">
-        <v>88.4549043800007</v>
+        <v>88.45490441688071</v>
       </c>
       <c r="N17">
-        <v>167.7019656100011</v>
+        <v>167.7019656975372</v>
       </c>
       <c r="O17">
-        <v>254.7542537</v>
+        <v>254.7542538487487</v>
       </c>
       <c r="P17">
-        <v>463.0797496400001</v>
+        <v>463.0797498996408</v>
       </c>
       <c r="S17">
         <v>11</v>
@@ -2244,19 +2244,19 @@
         <v>16</v>
       </c>
       <c r="U17">
-        <v>40.69097644199883</v>
+        <v>40.69097645875718</v>
       </c>
       <c r="V17">
-        <v>123.8967437800002</v>
+        <v>123.8967437879055</v>
       </c>
       <c r="W17">
-        <v>229.7804134000008</v>
+        <v>229.7804134097605</v>
       </c>
       <c r="X17">
-        <v>348.0666963400008</v>
+        <v>348.0666963783124</v>
       </c>
       <c r="Y17">
-        <v>607.6523356800008</v>
+        <v>607.6523358011382</v>
       </c>
       <c r="AB17">
         <v>11</v>
@@ -2265,19 +2265,19 @@
         <v>17</v>
       </c>
       <c r="AD17">
-        <v>33.03137651399993</v>
+        <v>33.03137649942255</v>
       </c>
       <c r="AE17">
-        <v>51.06537359999993</v>
+        <v>51.06537359054846</v>
       </c>
       <c r="AF17">
-        <v>103.9359778499997</v>
+        <v>103.9359777983327</v>
       </c>
       <c r="AG17">
-        <v>175.0275004599998</v>
+        <v>175.0275003689994</v>
       </c>
       <c r="AH17">
-        <v>349.2628448199998</v>
+        <v>349.2628446562067</v>
       </c>
       <c r="AK17">
         <v>11</v>
@@ -2286,19 +2286,19 @@
         <v>11</v>
       </c>
       <c r="AM17">
-        <v>103.262757192002</v>
+        <v>103.2627572471356</v>
       </c>
       <c r="AN17">
-        <v>104.6627566999996</v>
+        <v>104.6627567623509</v>
       </c>
       <c r="AO17">
-        <v>411.443182199997</v>
+        <v>411.443182423267</v>
       </c>
       <c r="AP17">
-        <v>759.6523726299965</v>
+        <v>759.652373060082</v>
       </c>
       <c r="AQ17">
-        <v>1648.577962169999</v>
+        <v>1648.57796309494</v>
       </c>
       <c r="AT17">
         <v>11</v>
@@ -2307,19 +2307,19 @@
         <v>12</v>
       </c>
       <c r="AV17">
-        <v>100.7694173279997</v>
+        <v>100.7694173746568</v>
       </c>
       <c r="AW17">
-        <v>98.71506754999972</v>
+        <v>98.71506760429476</v>
       </c>
       <c r="AX17">
-        <v>392.7817763599978</v>
+        <v>392.7817764440515</v>
       </c>
       <c r="AY17">
-        <v>739.1347812799995</v>
+        <v>739.1347814661003</v>
       </c>
       <c r="AZ17">
-        <v>1437.243405130001</v>
+        <v>1437.243405508507</v>
       </c>
     </row>
     <row r="18" spans="1:52">
@@ -2330,19 +2330,19 @@
         <v>14</v>
       </c>
       <c r="C18">
-        <v>-8.158659203999946</v>
+        <v>-8.158659191537367</v>
       </c>
       <c r="D18">
-        <v>4.195530080000026</v>
+        <v>4.195530097059304</v>
       </c>
       <c r="E18">
-        <v>9.391061079999986</v>
+        <v>9.391061104765299</v>
       </c>
       <c r="F18">
-        <v>15.58659019999993</v>
+        <v>15.58659023525354</v>
       </c>
       <c r="G18">
-        <v>29.77653623999993</v>
+        <v>29.77653628711062</v>
       </c>
       <c r="J18">
         <v>14</v>
@@ -2351,19 +2351,19 @@
         <v>15</v>
       </c>
       <c r="L18">
-        <v>-4.917320807999658</v>
+        <v>-4.917320804727751</v>
       </c>
       <c r="M18">
-        <v>43.57541683999944</v>
+        <v>43.5754168709027</v>
       </c>
       <c r="N18">
-        <v>78.95530583000027</v>
+        <v>78.95530588097517</v>
       </c>
       <c r="O18">
-        <v>117.9329604499999</v>
+        <v>117.9329605506027</v>
       </c>
       <c r="P18">
-        <v>213.6759746999996</v>
+        <v>213.6759748903655</v>
       </c>
       <c r="S18">
         <v>14</v>
@@ -2372,19 +2372,19 @@
         <v>16</v>
       </c>
       <c r="U18">
-        <v>13.67598128400004</v>
+        <v>13.67598126594476</v>
       </c>
       <c r="V18">
-        <v>64.96089616000017</v>
+        <v>64.96089616153995</v>
       </c>
       <c r="W18">
-        <v>120.9273786999993</v>
+        <v>120.9273786895314</v>
       </c>
       <c r="X18">
-        <v>177.8938641399996</v>
+        <v>177.8938641218592</v>
       </c>
       <c r="Y18">
-        <v>300.02236636</v>
+        <v>300.022366324115</v>
       </c>
       <c r="AB18">
         <v>14</v>
@@ -2393,19 +2393,19 @@
         <v>17</v>
       </c>
       <c r="AD18">
-        <v>16.31061551400012</v>
+        <v>16.3106155051637</v>
       </c>
       <c r="AE18">
-        <v>33.77653431999988</v>
+        <v>33.77653433093997</v>
       </c>
       <c r="AF18">
-        <v>76.54747519000034</v>
+        <v>76.54747524212848</v>
       </c>
       <c r="AG18">
-        <v>127.1117134499998</v>
+        <v>127.1117135111704</v>
       </c>
       <c r="AH18">
-        <v>248.0278999900001</v>
+        <v>248.0279001207705</v>
       </c>
       <c r="AK18">
         <v>14</v>
@@ -2414,19 +2414,19 @@
         <v>11</v>
       </c>
       <c r="AM18">
-        <v>56.73518626799887</v>
+        <v>56.73518628949205</v>
       </c>
       <c r="AN18">
-        <v>56.57541087000027</v>
+        <v>56.57541088236758</v>
       </c>
       <c r="AO18">
-        <v>221.5027593800005</v>
+        <v>221.5027594564108</v>
       </c>
       <c r="AP18">
-        <v>409.0222856000019</v>
+        <v>409.0222857149584</v>
       </c>
       <c r="AQ18">
-        <v>889.4132745700026</v>
+        <v>889.4132748348729</v>
       </c>
       <c r="AT18">
         <v>14</v>
@@ -2435,19 +2435,19 @@
         <v>12</v>
       </c>
       <c r="AV18">
-        <v>30.70056618000126</v>
+        <v>30.70056612949975</v>
       </c>
       <c r="AW18">
-        <v>88.94412339999872</v>
+        <v>88.94412346057197</v>
       </c>
       <c r="AX18">
-        <v>276.8212053399993</v>
+        <v>276.8212054151254</v>
       </c>
       <c r="AY18">
-        <v>489.6759330300001</v>
+        <v>489.6759329531487</v>
       </c>
       <c r="AZ18">
-        <v>916.6032942099991</v>
+        <v>916.6032941952708</v>
       </c>
     </row>
     <row r="19" spans="1:52">
@@ -2458,19 +2458,19 @@
         <v>14</v>
       </c>
       <c r="C19">
-        <v>-7.545763860000079</v>
+        <v>-7.545763826342181</v>
       </c>
       <c r="D19">
-        <v>8.821287739999775</v>
+        <v>8.821287765455736</v>
       </c>
       <c r="E19">
-        <v>17.14372021000031</v>
+        <v>17.14372024519412</v>
       </c>
       <c r="F19">
-        <v>28.95425522999983</v>
+        <v>28.95425529965451</v>
       </c>
       <c r="G19">
-        <v>56.55154784000001</v>
+        <v>56.55154799056118</v>
       </c>
       <c r="J19">
         <v>13</v>
@@ -2479,19 +2479,19 @@
         <v>15</v>
       </c>
       <c r="L19">
-        <v>-13.51848109199955</v>
+        <v>-13.51848124129765</v>
       </c>
       <c r="M19">
-        <v>61.02545895999992</v>
+        <v>61.025459099204</v>
       </c>
       <c r="N19">
-        <v>116.908105970002</v>
+        <v>116.9081062157511</v>
       </c>
       <c r="O19">
-        <v>180.8823646299988</v>
+        <v>180.8823649955157</v>
       </c>
       <c r="P19">
-        <v>339.2184436899997</v>
+        <v>339.2184442617609</v>
       </c>
       <c r="S19">
         <v>13</v>
@@ -2500,19 +2500,19 @@
         <v>16</v>
       </c>
       <c r="U19">
-        <v>24.68205491400022</v>
+        <v>24.68205503391073</v>
       </c>
       <c r="V19">
-        <v>105.7822121499994</v>
+        <v>105.78221251993</v>
       </c>
       <c r="W19">
-        <v>195.8288577999992</v>
+        <v>195.8288584765833</v>
       </c>
       <c r="X19">
-        <v>295.8302136599996</v>
+        <v>295.830214677263</v>
       </c>
       <c r="Y19">
-        <v>510.4400705999988</v>
+        <v>510.4400723578956</v>
       </c>
       <c r="AB19">
         <v>13</v>
@@ -2521,19 +2521,19 @@
         <v>17</v>
       </c>
       <c r="AD19">
-        <v>29.81744890800019</v>
+        <v>29.81744898513352</v>
       </c>
       <c r="AE19">
-        <v>55.0419522000002</v>
+        <v>55.04195234413964</v>
       </c>
       <c r="AF19">
-        <v>114.62319536</v>
+        <v>114.6231956518918</v>
       </c>
       <c r="AG19">
-        <v>188.7850950100001</v>
+        <v>188.7850954861542</v>
       </c>
       <c r="AH19">
-        <v>376.3439454099998</v>
+        <v>376.3439463622321</v>
       </c>
       <c r="AK19">
         <v>13</v>
@@ -2542,19 +2542,19 @@
         <v>11</v>
       </c>
       <c r="AM19">
-        <v>96.44439147600131</v>
+        <v>96.44439183035138</v>
       </c>
       <c r="AN19">
-        <v>97.78196519000268</v>
+        <v>97.78196553000453</v>
       </c>
       <c r="AO19">
-        <v>378.5983956300006</v>
+        <v>378.598397009664</v>
       </c>
       <c r="AP19">
-        <v>701.6939621300044</v>
+        <v>701.693964692935</v>
       </c>
       <c r="AQ19">
-        <v>1518.862478669998</v>
+        <v>1518.862484237205</v>
       </c>
       <c r="AT19">
         <v>13</v>
@@ -2563,19 +2563,19 @@
         <v>12</v>
       </c>
       <c r="AV19">
-        <v>79.4699301239998</v>
+        <v>79.46993025796655</v>
       </c>
       <c r="AW19">
-        <v>98.33532223999828</v>
+        <v>98.33532271301556</v>
       </c>
       <c r="AX19">
-        <v>366.0288991900016</v>
+        <v>366.0289005631639</v>
       </c>
       <c r="AY19">
-        <v>686.2569729299994</v>
+        <v>686.2569752457275</v>
       </c>
       <c r="AZ19">
-        <v>1339.301744290002</v>
+        <v>1339.301748704402</v>
       </c>
     </row>
     <row r="20" spans="1:52">
@@ -2586,19 +2586,19 @@
         <v>14</v>
       </c>
       <c r="C20">
-        <v>-71.65577855399988</v>
+        <v>-71.65577841904997</v>
       </c>
       <c r="D20">
-        <v>-7.286874960002024</v>
+        <v>-7.286874953620099</v>
       </c>
       <c r="E20">
-        <v>0.4262540200006697</v>
+        <v>0.4262540255613203</v>
       </c>
       <c r="F20">
-        <v>9.852501389999816</v>
+        <v>9.852501391157602</v>
       </c>
       <c r="G20">
-        <v>69.41814442000032</v>
+        <v>69.41814433547643</v>
       </c>
       <c r="J20">
         <v>12</v>
@@ -2607,19 +2607,19 @@
         <v>15</v>
       </c>
       <c r="L20">
-        <v>-34.96726979999949</v>
+        <v>-34.96726970300369</v>
       </c>
       <c r="M20">
-        <v>149.9919340499964</v>
+        <v>149.991933816169</v>
       </c>
       <c r="N20">
-        <v>304.9838655499971</v>
+        <v>304.9838650887068</v>
       </c>
       <c r="O20">
-        <v>476.1151733000006</v>
+        <v>476.1151726355947</v>
       </c>
       <c r="P20">
-        <v>910.5171886499992</v>
+        <v>910.5171873834151</v>
       </c>
       <c r="S20">
         <v>12</v>
@@ -2628,19 +2628,19 @@
         <v>16</v>
       </c>
       <c r="U20">
-        <v>84.33941932800553</v>
+        <v>84.33941917585071</v>
       </c>
       <c r="V20">
-        <v>212.69696578</v>
+        <v>212.696965382178</v>
       </c>
       <c r="W20">
-        <v>404.6808035099984</v>
+        <v>404.6808027084171</v>
       </c>
       <c r="X20">
-        <v>629.3777830100007</v>
+        <v>629.3777817618138</v>
       </c>
       <c r="Y20">
-        <v>1146.763636190002</v>
+        <v>1146.763633872955</v>
       </c>
       <c r="AB20">
         <v>12</v>
@@ -2649,19 +2649,19 @@
         <v>17</v>
       </c>
       <c r="AD20">
-        <v>64.02302048999991</v>
+        <v>64.02302033785145</v>
       </c>
       <c r="AE20">
-        <v>91.41814393999994</v>
+        <v>91.41814375381182</v>
       </c>
       <c r="AF20">
-        <v>195.836294499999</v>
+        <v>195.8362940720763</v>
       </c>
       <c r="AG20">
-        <v>331.6807099700009</v>
+        <v>331.6807092438994</v>
       </c>
       <c r="AH20">
-        <v>648.3614147999997</v>
+        <v>648.3614133650281</v>
       </c>
       <c r="AK20">
         <v>12</v>
@@ -2670,19 +2670,19 @@
         <v>11</v>
       </c>
       <c r="AM20">
-        <v>230.3707889040016</v>
+        <v>230.3707882763556</v>
       </c>
       <c r="AN20">
-        <v>237.5412898400027</v>
+        <v>237.541289223991</v>
       </c>
       <c r="AO20">
-        <v>916.0257774999992</v>
+        <v>916.02577501427</v>
       </c>
       <c r="AP20">
-        <v>1700.354657690004</v>
+        <v>1700.354653059905</v>
       </c>
       <c r="AQ20">
-        <v>3685.242488760006</v>
+        <v>3685.242478757638</v>
       </c>
       <c r="AT20">
         <v>12</v>
@@ -2691,19 +2691,19 @@
         <v>12</v>
       </c>
       <c r="AV20">
-        <v>91.70666608799364</v>
+        <v>91.70666588079619</v>
       </c>
       <c r="AW20">
-        <v>134.2787969899982</v>
+        <v>134.2787970219724</v>
       </c>
       <c r="AX20">
-        <v>651.3777573800035</v>
+        <v>651.3777563354597</v>
       </c>
       <c r="AY20">
-        <v>1306.755533469997</v>
+        <v>1306.755530944487</v>
       </c>
       <c r="AZ20">
-        <v>2709.347304490009</v>
+        <v>2709.3472990921</v>
       </c>
     </row>
     <row r="21" spans="1:52">
@@ -2714,19 +2714,19 @@
         <v>14</v>
       </c>
       <c r="C21">
-        <v>-226.1998232759997</v>
+        <v>-226.1998232169517</v>
       </c>
       <c r="D21">
-        <v>-62.99994825000067</v>
+        <v>-62.99994823949055</v>
       </c>
       <c r="E21">
-        <v>-87.99991579000016</v>
+        <v>-87.99991576984212</v>
       </c>
       <c r="F21">
-        <v>-129.9998705100006</v>
+        <v>-129.9998704783302</v>
       </c>
       <c r="G21">
-        <v>-102.9998697899991</v>
+        <v>-102.9998697684587</v>
       </c>
       <c r="J21">
         <v>28</v>
@@ -2735,19 +2735,19 @@
         <v>15</v>
       </c>
       <c r="L21">
-        <v>32.39998368000306</v>
+        <v>32.39998367466978</v>
       </c>
       <c r="M21">
-        <v>248.9998385299987</v>
+        <v>248.9998384336541</v>
       </c>
       <c r="N21">
-        <v>488.9996790800033</v>
+        <v>488.9996788876233</v>
       </c>
       <c r="O21">
-        <v>767.9994941500008</v>
+        <v>767.9994938582167</v>
       </c>
       <c r="P21">
-        <v>1478.999013829998</v>
+        <v>1478.99901331533</v>
       </c>
       <c r="S21">
         <v>28</v>
@@ -2756,19 +2756,19 @@
         <v>16</v>
       </c>
       <c r="U21">
-        <v>193.1998457219997</v>
+        <v>193.1998456687343</v>
       </c>
       <c r="V21">
-        <v>305.9997687999985</v>
+        <v>305.9997687062787</v>
       </c>
       <c r="W21">
-        <v>596.9995387700001</v>
+        <v>596.9995385969723</v>
       </c>
       <c r="X21">
-        <v>968.9992422500018</v>
+        <v>968.999241988884</v>
       </c>
       <c r="Y21">
-        <v>1846.99854477</v>
+        <v>1846.998544326174</v>
       </c>
       <c r="AB21">
         <v>28</v>
@@ -2777,19 +2777,19 @@
         <v>17</v>
       </c>
       <c r="AD21">
-        <v>83.99992892999944</v>
+        <v>83.99992891172633</v>
       </c>
       <c r="AE21">
-        <v>68.99994814999991</v>
+        <v>68.99994811790793</v>
       </c>
       <c r="AF21">
-        <v>151.99988605</v>
+        <v>151.9998859887128</v>
       </c>
       <c r="AG21">
-        <v>276.9997884200002</v>
+        <v>276.9997883169353</v>
       </c>
       <c r="AH21">
-        <v>535.9995822299998</v>
+        <v>535.9995820324511</v>
       </c>
       <c r="AK21">
         <v>28</v>
@@ -2798,19 +2798,19 @@
         <v>11</v>
       </c>
       <c r="AM21">
-        <v>357.5997178319813</v>
+        <v>357.5997177195386</v>
       </c>
       <c r="AN21">
-        <v>363.9997201000006</v>
+        <v>363.9997199787977</v>
       </c>
       <c r="AO21">
-        <v>1414.9989088</v>
+        <v>1414.998908351554</v>
       </c>
       <c r="AP21">
-        <v>2620.99797569</v>
+        <v>2620.997974853796</v>
       </c>
       <c r="AQ21">
-        <v>5689.995606350014</v>
+        <v>5689.995604530108</v>
       </c>
       <c r="AT21">
         <v>28</v>
@@ -2819,19 +2819,19 @@
         <v>12</v>
       </c>
       <c r="AV21">
-        <v>279.5997609120022</v>
+        <v>279.599760833793</v>
       </c>
       <c r="AW21">
-        <v>36.00005812000018</v>
+        <v>36.00005794495519</v>
       </c>
       <c r="AX21">
-        <v>808.9994281799954</v>
+        <v>808.9994278730155</v>
       </c>
       <c r="AY21">
-        <v>1868.99860585</v>
+        <v>1868.998605258806</v>
       </c>
       <c r="AZ21">
-        <v>4004.996917389995</v>
+        <v>4004.996916342694</v>
       </c>
     </row>
     <row r="22" spans="1:52">
@@ -2842,19 +2842,19 @@
         <v>14</v>
       </c>
       <c r="C22">
-        <v>-111.4740859020012</v>
+        <v>-111.4740859528138</v>
       </c>
       <c r="D22">
-        <v>21.64333596999859</v>
+        <v>21.64333598371741</v>
       </c>
       <c r="E22">
-        <v>47.93002307999996</v>
+        <v>47.93002309188432</v>
       </c>
       <c r="F22">
-        <v>56.57336632999977</v>
+        <v>56.57336634229614</v>
       </c>
       <c r="G22">
-        <v>125.4334579599999</v>
+        <v>125.4334579571978</v>
       </c>
       <c r="J22">
         <v>18</v>
@@ -2863,19 +2863,19 @@
         <v>15</v>
       </c>
       <c r="L22">
-        <v>-8.102082780000273</v>
+        <v>-8.102082728302776</v>
       </c>
       <c r="M22">
-        <v>280.2236185700021</v>
+        <v>280.2236185973343</v>
       </c>
       <c r="N22">
-        <v>547.1605361200018</v>
+        <v>547.1605361587172</v>
       </c>
       <c r="O22">
-        <v>816.0974586899974</v>
+        <v>816.0974587616693</v>
       </c>
       <c r="P22">
-        <v>1445.11811222</v>
+        <v>1445.118112371994</v>
       </c>
       <c r="S22">
         <v>18</v>
@@ -2884,19 +2884,19 @@
         <v>16</v>
       </c>
       <c r="U22">
-        <v>127.8041466899995</v>
+        <v>127.8041466757568</v>
       </c>
       <c r="V22">
-        <v>305.7271049400024</v>
+        <v>305.7271048315397</v>
       </c>
       <c r="W22">
-        <v>588.2374611499999</v>
+        <v>588.2374609328654</v>
       </c>
       <c r="X22">
-        <v>921.9645774400014</v>
+        <v>921.9645771184188</v>
       </c>
       <c r="Y22">
-        <v>1678.705513490002</v>
+        <v>1678.705512924424</v>
       </c>
       <c r="AB22">
         <v>18</v>
@@ -2905,19 +2905,19 @@
         <v>17</v>
       </c>
       <c r="AD22">
-        <v>59.23212730800015</v>
+        <v>59.23212728771523</v>
       </c>
       <c r="AE22">
-        <v>87.07684392999909</v>
+        <v>87.07684390473514</v>
       </c>
       <c r="AF22">
-        <v>181.4403960900013</v>
+        <v>181.4403960109294</v>
       </c>
       <c r="AG22">
-        <v>311.7339994399995</v>
+        <v>311.7339992748593</v>
       </c>
       <c r="AH22">
-        <v>581.2512540999996</v>
+        <v>581.2512537797484</v>
       </c>
       <c r="AK22">
         <v>18</v>
@@ -2926,19 +2926,19 @@
         <v>11</v>
       </c>
       <c r="AM22">
-        <v>159.9523537499954</v>
+        <v>159.9523537980567</v>
       </c>
       <c r="AN22">
-        <v>163.2236849899928</v>
+        <v>163.2236850301415</v>
       </c>
       <c r="AO22">
-        <v>638.8947315699988</v>
+        <v>638.8947317601414</v>
       </c>
       <c r="AP22">
-        <v>1183.712588699997</v>
+        <v>1183.712589073984</v>
       </c>
       <c r="AQ22">
-        <v>2566.865625680006</v>
+        <v>2566.865626476814</v>
       </c>
       <c r="AT22">
         <v>18</v>
@@ -2947,19 +2947,19 @@
         <v>12</v>
       </c>
       <c r="AV22">
-        <v>187.0362773280031</v>
+        <v>187.0362773153284</v>
       </c>
       <c r="AW22">
-        <v>460.2304409399985</v>
+        <v>460.2304408897762</v>
       </c>
       <c r="AX22">
-        <v>1157.761522469995</v>
+        <v>1157.761522269168</v>
       </c>
       <c r="AY22">
-        <v>2070.509312010003</v>
+        <v>2070.509311640562</v>
       </c>
       <c r="AZ22">
-        <v>3849.151768600001</v>
+        <v>3849.151767798227</v>
       </c>
     </row>
     <row r="23" spans="1:52">
@@ -2970,19 +2970,19 @@
         <v>14</v>
       </c>
       <c r="C23">
-        <v>-9.313017882000167</v>
+        <v>-9.313017899953593</v>
       </c>
       <c r="D23">
-        <v>7.207149919999892</v>
+        <v>7.207149914364209</v>
       </c>
       <c r="E23">
-        <v>15.20714588999976</v>
+        <v>15.20714587300108</v>
       </c>
       <c r="F23">
-        <v>21.99998232999997</v>
+        <v>21.99998231021744</v>
       </c>
       <c r="G23">
-        <v>48.03576129999976</v>
+        <v>48.03576127742372</v>
       </c>
       <c r="J23">
         <v>19</v>
@@ -2991,19 +2991,19 @@
         <v>15</v>
       </c>
       <c r="L23">
-        <v>-9.372883529999401</v>
+        <v>-9.372883539241229</v>
       </c>
       <c r="M23">
-        <v>55.97177628999998</v>
+        <v>55.97177630652732</v>
       </c>
       <c r="N23">
-        <v>103.5292421000004</v>
+        <v>103.5292421103622</v>
       </c>
       <c r="O23">
-        <v>155.5010214199992</v>
+        <v>155.5010214337603</v>
       </c>
       <c r="P23">
-        <v>285.6875170299995</v>
+        <v>285.687517034306</v>
       </c>
       <c r="S23">
         <v>19</v>
@@ -3012,19 +3012,19 @@
         <v>16</v>
       </c>
       <c r="U23">
-        <v>16.76160736800011</v>
+        <v>16.7616073645595</v>
       </c>
       <c r="V23">
-        <v>83.00755690000142</v>
+        <v>83.00755685783315</v>
       </c>
       <c r="W23">
-        <v>153.18649</v>
+        <v>153.1864899248039</v>
       </c>
       <c r="X23">
-        <v>231.1940521100009</v>
+        <v>231.194052019157</v>
       </c>
       <c r="Y23">
-        <v>403.0377989599992</v>
+        <v>403.0377987917582</v>
       </c>
       <c r="AB23">
         <v>19</v>
@@ -3033,19 +3033,19 @@
         <v>17</v>
       </c>
       <c r="AD23">
-        <v>24.41582434800035</v>
+        <v>24.41582433921121</v>
       </c>
       <c r="AE23">
-        <v>46.48587220999934</v>
+        <v>46.48587217928343</v>
       </c>
       <c r="AF23">
-        <v>98.17889850999973</v>
+        <v>98.1788984795494</v>
       </c>
       <c r="AG23">
-        <v>163.7005500699997</v>
+        <v>163.7005500162932</v>
       </c>
       <c r="AH23">
-        <v>321.1939459700006</v>
+        <v>321.1939458716993</v>
       </c>
       <c r="AK23">
         <v>19</v>
@@ -3054,19 +3054,19 @@
         <v>11</v>
       </c>
       <c r="AM23">
-        <v>57.87460122599987</v>
+        <v>57.87460129213832</v>
       </c>
       <c r="AN23">
-        <v>60.35030336999989</v>
+        <v>60.35030343865401</v>
       </c>
       <c r="AO23">
-        <v>229.401225309999</v>
+        <v>229.4012255607922</v>
       </c>
       <c r="AP23">
-        <v>424.1094041900014</v>
+        <v>424.1094046700473</v>
       </c>
       <c r="AQ23">
-        <v>920.8120579300012</v>
+        <v>920.812058959782</v>
       </c>
       <c r="AT23">
         <v>19</v>
@@ -3075,19 +3075,19 @@
         <v>12</v>
       </c>
       <c r="AV23">
-        <v>65.07458892000068</v>
+        <v>65.07458886019776</v>
       </c>
       <c r="AW23">
-        <v>84.55745188999754</v>
+        <v>84.5574517008663</v>
       </c>
       <c r="AX23">
-        <v>304.3013625699969</v>
+        <v>304.3013623589995</v>
       </c>
       <c r="AY23">
-        <v>564.909690550001</v>
+        <v>564.9096901786761</v>
       </c>
       <c r="AZ23">
-        <v>1068.640481750001</v>
+        <v>1068.640481175842</v>
       </c>
     </row>
     <row r="24" spans="1:52">
@@ -3098,19 +3098,19 @@
         <v>14</v>
       </c>
       <c r="C24">
-        <v>-45.00005039999951</v>
+        <v>-45.00005045547141</v>
       </c>
       <c r="D24">
-        <v>19.98703904999957</v>
+        <v>19.98703902486022</v>
       </c>
       <c r="E24">
-        <v>36.37669772000027</v>
+        <v>36.3766977012765</v>
       </c>
       <c r="F24">
-        <v>57.76638752999952</v>
+        <v>57.76638749669655</v>
       </c>
       <c r="G24">
-        <v>123.3379300900001</v>
+        <v>123.3379300383281</v>
       </c>
       <c r="J24">
         <v>20</v>
@@ -3119,19 +3119,19 @@
         <v>15</v>
       </c>
       <c r="L24">
-        <v>-15.5922279360002</v>
+        <v>-15.59222793051776</v>
       </c>
       <c r="M24">
-        <v>167.5457418500009</v>
+        <v>167.5457418892456</v>
       </c>
       <c r="N24">
-        <v>318.2994105300004</v>
+        <v>318.2994106163496</v>
       </c>
       <c r="O24">
-        <v>485.2478892899999</v>
+        <v>485.2478894282904</v>
       </c>
       <c r="P24">
-        <v>890.9241890900012</v>
+        <v>890.9241893036069</v>
       </c>
       <c r="S24">
         <v>20</v>
@@ -3140,19 +3140,19 @@
         <v>16</v>
       </c>
       <c r="U24">
-        <v>74.50916012999915</v>
+        <v>74.50916016967494</v>
       </c>
       <c r="V24">
-        <v>242.1043236700007</v>
+        <v>242.1043236782134</v>
       </c>
       <c r="W24">
-        <v>448.2216527800029</v>
+        <v>448.2216528009449</v>
       </c>
       <c r="X24">
-        <v>681.9363677800029</v>
+        <v>681.9363678423888</v>
       </c>
       <c r="Y24">
-        <v>1205.352947849999</v>
+        <v>1205.352947947458</v>
       </c>
       <c r="AB24">
         <v>20</v>
@@ -3161,19 +3161,19 @@
         <v>17</v>
       </c>
       <c r="AD24">
-        <v>65.96889312599978</v>
+        <v>65.9688931197561</v>
       </c>
       <c r="AE24">
-        <v>102.9352342099992</v>
+        <v>102.9352342131842</v>
       </c>
       <c r="AF24">
-        <v>213.0652763199996</v>
+        <v>213.0652763251456</v>
       </c>
       <c r="AG24">
-        <v>352.9745892700003</v>
+        <v>352.9745892436358</v>
       </c>
       <c r="AH24">
-        <v>682.7411397400001</v>
+        <v>682.7411396916868</v>
       </c>
       <c r="AK24">
         <v>20</v>
@@ -3182,19 +3182,19 @@
         <v>11</v>
       </c>
       <c r="AM24">
-        <v>202.1380942380056</v>
+        <v>202.1380944757402</v>
       </c>
       <c r="AN24">
-        <v>203.3380876200027</v>
+        <v>203.3380878525059</v>
       </c>
       <c r="AO24">
-        <v>792.5601597799978</v>
+        <v>792.5601607121789</v>
       </c>
       <c r="AP24">
-        <v>1473.35384453999</v>
+        <v>1473.353846254366</v>
       </c>
       <c r="AQ24">
-        <v>3194.435512929995</v>
+        <v>3194.43551665773</v>
       </c>
       <c r="AT24">
         <v>20</v>
@@ -3203,19 +3203,19 @@
         <v>12</v>
       </c>
       <c r="AV24">
-        <v>209.4314113080036</v>
+        <v>209.4314112668217</v>
       </c>
       <c r="AW24">
-        <v>218.285811380003</v>
+        <v>218.2858113717157</v>
       </c>
       <c r="AX24">
-        <v>811.2217826600026</v>
+        <v>811.2217828156718</v>
       </c>
       <c r="AY24">
-        <v>1521.872415039994</v>
+        <v>1521.872415189602</v>
       </c>
       <c r="AZ24">
-        <v>2898.770058809998</v>
+        <v>2898.770059003626</v>
       </c>
     </row>
     <row r="25" spans="1:52">
@@ -3226,19 +3226,19 @@
         <v>14</v>
       </c>
       <c r="C25">
-        <v>-200.4000010140008</v>
+        <v>-200.4000012648194</v>
       </c>
       <c r="D25">
-        <v>35.99998052999945</v>
+        <v>35.99998046913242</v>
       </c>
       <c r="E25">
-        <v>85.99994748000063</v>
+        <v>85.99994734184656</v>
       </c>
       <c r="F25">
-        <v>123.9999217599998</v>
+        <v>123.9999215518146</v>
       </c>
       <c r="G25">
-        <v>305.9998643900017</v>
+        <v>305.9998641037255</v>
       </c>
       <c r="J25">
         <v>27</v>
@@ -3247,19 +3247,19 @@
         <v>15</v>
       </c>
       <c r="L25">
-        <v>-43.19997597600377</v>
+        <v>-43.19997594060988</v>
       </c>
       <c r="M25">
-        <v>502.99987633001</v>
+        <v>502.9998764525953</v>
       </c>
       <c r="N25">
-        <v>953.99976314999</v>
+        <v>953.9997633622406</v>
       </c>
       <c r="O25">
-        <v>1436.999649890004</v>
+        <v>1436.999650181962</v>
       </c>
       <c r="P25">
-        <v>2561.999382690003</v>
+        <v>2561.999383157563</v>
       </c>
       <c r="S25">
         <v>27</v>
@@ -3268,19 +3268,19 @@
         <v>16</v>
       </c>
       <c r="U25">
-        <v>272.9999655659994</v>
+        <v>272.9999657508633</v>
       </c>
       <c r="V25">
-        <v>701.9997775499942</v>
+        <v>701.9997774597941</v>
       </c>
       <c r="W25">
-        <v>1325.999595950001</v>
+        <v>1325.999595795602</v>
       </c>
       <c r="X25">
-        <v>2038.999403880007</v>
+        <v>2038.999403713762</v>
       </c>
       <c r="Y25">
-        <v>3599.99902073</v>
+        <v>3599.999020598811</v>
       </c>
       <c r="AB25">
         <v>27</v>
@@ -3289,19 +3289,19 @@
         <v>17</v>
       </c>
       <c r="AD25">
-        <v>164.3999397060015</v>
+        <v>164.3999396893523</v>
       </c>
       <c r="AE25">
-        <v>213.9998685400005</v>
+        <v>213.9998683736667</v>
       </c>
       <c r="AF25">
-        <v>453.9997326499979</v>
+        <v>453.9997323127445</v>
       </c>
       <c r="AG25">
-        <v>761.9995580599989</v>
+        <v>761.9995575236881</v>
       </c>
       <c r="AH25">
-        <v>1468.999120300005</v>
+        <v>1468.999119203512</v>
       </c>
       <c r="AK25">
         <v>27</v>
@@ -3310,19 +3310,19 @@
         <v>11</v>
       </c>
       <c r="AM25">
-        <v>595.7999990400131</v>
+        <v>595.8000000153552</v>
       </c>
       <c r="AN25">
-        <v>608.0000089499954</v>
+        <v>608.0000099440076</v>
       </c>
       <c r="AO25">
-        <v>2369.000001840017</v>
+        <v>2369.000005717098</v>
       </c>
       <c r="AP25">
-        <v>4388.000000950007</v>
+        <v>4388.000008133982</v>
       </c>
       <c r="AQ25">
-        <v>9519.000001640001</v>
+        <v>9519.000017216094</v>
       </c>
       <c r="AT25">
         <v>27</v>
@@ -3331,19 +3331,19 @@
         <v>12</v>
       </c>
       <c r="AV25">
-        <v>556.7998329840048</v>
+        <v>556.7998330087139</v>
       </c>
       <c r="AW25">
-        <v>563.9996964500024</v>
+        <v>563.9996959739656</v>
       </c>
       <c r="AX25">
-        <v>2370.999156250007</v>
+        <v>2370.999155720652</v>
       </c>
       <c r="AY25">
-        <v>4471.998361760008</v>
+        <v>4471.998360978832</v>
       </c>
       <c r="AZ25">
-        <v>8573.996879309969</v>
+        <v>8573.996877831931</v>
       </c>
     </row>
     <row r="26" spans="1:52">
@@ -3354,19 +3354,19 @@
         <v>14</v>
       </c>
       <c r="C26">
-        <v>-76.51701403799916</v>
+        <v>-76.51701415461048</v>
       </c>
       <c r="D26">
-        <v>8.283342189999985</v>
+        <v>8.283342167972933</v>
       </c>
       <c r="E26">
-        <v>18.61788376999993</v>
+        <v>18.6178837276384</v>
       </c>
       <c r="F26">
-        <v>22.46430892999933</v>
+        <v>22.46430887003589</v>
       </c>
       <c r="G26">
-        <v>66.18092444000058</v>
+        <v>66.18092435600693</v>
       </c>
       <c r="J26">
         <v>22</v>
@@ -3375,19 +3375,19 @@
         <v>15</v>
       </c>
       <c r="L26">
-        <v>-1.87568127600025</v>
+        <v>-1.875681203224304</v>
       </c>
       <c r="M26">
-        <v>160.8116642900004</v>
+        <v>160.8116644351758</v>
       </c>
       <c r="N26">
-        <v>299.2138370700013</v>
+        <v>299.2138373104117</v>
       </c>
       <c r="O26">
-        <v>453.0766913100033</v>
+        <v>453.0766916557586</v>
       </c>
       <c r="P26">
-        <v>824.8333898500005</v>
+        <v>824.8333904673527</v>
       </c>
       <c r="S26">
         <v>22</v>
@@ -3396,19 +3396,19 @@
         <v>16</v>
       </c>
       <c r="U26">
-        <v>94.03766806799922</v>
+        <v>94.03766815912604</v>
       </c>
       <c r="V26">
-        <v>202.47342579</v>
+        <v>202.4734257921646</v>
       </c>
       <c r="W26">
-        <v>387.0254651699988</v>
+        <v>387.0254651989262</v>
       </c>
       <c r="X26">
-        <v>600.7274380799981</v>
+        <v>600.7274381749712</v>
       </c>
       <c r="Y26">
-        <v>1086.076511550002</v>
+        <v>1086.076511823895</v>
       </c>
       <c r="AB26">
         <v>22</v>
@@ -3417,19 +3417,19 @@
         <v>17</v>
       </c>
       <c r="AD26">
-        <v>49.4906438579992</v>
+        <v>49.49064383569885</v>
       </c>
       <c r="AE26">
-        <v>58.79518658999905</v>
+        <v>58.79518652243041</v>
       </c>
       <c r="AF26">
-        <v>126.0510594799998</v>
+        <v>126.05105932579</v>
       </c>
       <c r="AG26">
-        <v>213.4878937899998</v>
+        <v>213.4878935587853</v>
       </c>
       <c r="AH26">
-        <v>407.3067184399988</v>
+        <v>407.3067179635823</v>
       </c>
       <c r="AK26">
         <v>22</v>
@@ -3438,19 +3438,19 @@
         <v>11</v>
       </c>
       <c r="AM26">
-        <v>176.0567487060034</v>
+        <v>176.0567489095811</v>
       </c>
       <c r="AN26">
-        <v>178.3401012500071</v>
+        <v>178.3401014666633</v>
       </c>
       <c r="AO26">
-        <v>693.1282524200069</v>
+        <v>693.1282532438818</v>
       </c>
       <c r="AP26">
-        <v>1281.369814270009</v>
+        <v>1281.369815784521</v>
       </c>
       <c r="AQ26">
-        <v>2782.253425160001</v>
+        <v>2782.253428421031</v>
       </c>
       <c r="AT26">
         <v>22</v>
@@ -3459,19 +3459,19 @@
         <v>12</v>
       </c>
       <c r="AV26">
-        <v>159.5461946579962</v>
+        <v>159.5461946502874</v>
       </c>
       <c r="AW26">
-        <v>173.1296792299872</v>
+        <v>173.129679353533</v>
       </c>
       <c r="AX26">
-        <v>686.6797916199976</v>
+        <v>686.6797917228178</v>
       </c>
       <c r="AY26">
-        <v>1295.189646409999</v>
+        <v>1295.189646669354</v>
       </c>
       <c r="AZ26">
-        <v>2464.457926679999</v>
+        <v>2464.457926890318</v>
       </c>
     </row>
     <row r="27" spans="1:52">
@@ -3482,19 +3482,19 @@
         <v>14</v>
       </c>
       <c r="C27">
-        <v>-154.1999762040014</v>
+        <v>-154.1999762408341</v>
       </c>
       <c r="D27">
-        <v>20.99999862000004</v>
+        <v>20.99999859827585</v>
       </c>
       <c r="E27">
-        <v>59.00000292999903</v>
+        <v>59.00000288609954</v>
       </c>
       <c r="F27">
-        <v>77.00000705000093</v>
+        <v>77.00000694900518</v>
       </c>
       <c r="G27">
-        <v>211.9999811800008</v>
+        <v>211.9999810090285</v>
       </c>
       <c r="J27">
         <v>29</v>
@@ -3503,19 +3503,19 @@
         <v>15</v>
       </c>
       <c r="L27">
-        <v>-44.3999349600017</v>
+        <v>-44.39993493480506</v>
       </c>
       <c r="M27">
-        <v>377.9999396699968</v>
+        <v>377.9999395769955</v>
       </c>
       <c r="N27">
-        <v>730.9998759699993</v>
+        <v>730.9998757921858</v>
       </c>
       <c r="O27">
-        <v>1108.999857660001</v>
+        <v>1108.999857266295</v>
       </c>
       <c r="P27">
-        <v>1991.99972761</v>
+        <v>1991.999726908478</v>
       </c>
       <c r="S27">
         <v>29</v>
@@ -3524,19 +3524,19 @@
         <v>16</v>
       </c>
       <c r="U27">
-        <v>198.5999310299976</v>
+        <v>198.5999310406678</v>
       </c>
       <c r="V27">
-        <v>457.9998452</v>
+        <v>457.9998449823979</v>
       </c>
       <c r="W27">
-        <v>880.9997143000001</v>
+        <v>880.9997139194347</v>
       </c>
       <c r="X27">
-        <v>1357.999567710001</v>
+        <v>1357.999567191215</v>
       </c>
       <c r="Y27">
-        <v>2419.999283609999</v>
+        <v>2419.999282740318</v>
       </c>
       <c r="AB27">
         <v>29</v>
@@ -3545,19 +3545,19 @@
         <v>17</v>
       </c>
       <c r="AD27">
-        <v>125.9999382659989</v>
+        <v>125.9999382149899</v>
       </c>
       <c r="AE27">
-        <v>163.9999260200011</v>
+        <v>163.9999258908574</v>
       </c>
       <c r="AF27">
-        <v>343.9998457200008</v>
+        <v>343.9998454652441</v>
       </c>
       <c r="AG27">
-        <v>578.999728929999</v>
+        <v>578.9997285537065</v>
       </c>
       <c r="AH27">
-        <v>1125.999488490002</v>
+        <v>1125.999487665224</v>
       </c>
       <c r="AK27">
         <v>29</v>
@@ -3566,19 +3566,19 @@
         <v>11</v>
       </c>
       <c r="AM27">
-        <v>433.1998323660082</v>
+        <v>433.1998319713021</v>
       </c>
       <c r="AN27">
-        <v>439.9998468799895</v>
+        <v>439.9998464807577</v>
       </c>
       <c r="AO27">
-        <v>1728.999369180005</v>
+        <v>1728.999367596901</v>
       </c>
       <c r="AP27">
-        <v>3198.99881818</v>
+        <v>3198.998815235333</v>
       </c>
       <c r="AQ27">
-        <v>6947.997418610001</v>
+        <v>6947.997412228666</v>
       </c>
       <c r="AT27">
         <v>29</v>
@@ -3587,19 +3587,19 @@
         <v>12</v>
       </c>
       <c r="AV27">
-        <v>379.1998425359998</v>
+        <v>379.1998424830963</v>
       </c>
       <c r="AW27">
-        <v>310.0000196999899</v>
+        <v>310.0000195852845</v>
       </c>
       <c r="AX27">
-        <v>1401.999790429996</v>
+        <v>1401.99978969041</v>
       </c>
       <c r="AY27">
-        <v>2929.999214399999</v>
+        <v>2929.999213709744</v>
       </c>
       <c r="AZ27">
-        <v>5603.998524559982</v>
+        <v>5603.998522622016</v>
       </c>
     </row>
     <row r="28" spans="1:52">
@@ -3610,19 +3610,19 @@
         <v>14</v>
       </c>
       <c r="C28">
-        <v>-25.19924489400045</v>
+        <v>-25.19924483945897</v>
       </c>
       <c r="D28">
-        <v>-1.99994592999974</v>
+        <v>-1.999945893799122</v>
       </c>
       <c r="E28">
-        <v>-0.9999754700002086</v>
+        <v>-0.9999754118666716</v>
       </c>
       <c r="F28">
-        <v>1.999821310000243</v>
+        <v>1.999821400835572</v>
       </c>
       <c r="G28">
-        <v>21.99909972999967</v>
+        <v>21.99909986594184</v>
       </c>
       <c r="J28">
         <v>21</v>
@@ -3631,19 +3631,19 @@
         <v>15</v>
       </c>
       <c r="L28">
-        <v>-19.79918835600074</v>
+        <v>-19.79918835940134</v>
       </c>
       <c r="M28">
-        <v>53.99824463999994</v>
+        <v>53.9982446612712</v>
       </c>
       <c r="N28">
-        <v>106.9965363699994</v>
+        <v>106.9965364311165</v>
       </c>
       <c r="O28">
-        <v>163.9948719700005</v>
+        <v>163.9948721017709</v>
       </c>
       <c r="P28">
-        <v>311.9898752299996</v>
+        <v>311.9898754019014</v>
       </c>
       <c r="S28">
         <v>21</v>
@@ -3652,19 +3652,19 @@
         <v>16</v>
       </c>
       <c r="U28">
-        <v>31.7989373520004</v>
+        <v>31.79893731077027</v>
       </c>
       <c r="V28">
-        <v>89.99684436999814</v>
+        <v>89.99684438881741</v>
       </c>
       <c r="W28">
-        <v>171.9938930600001</v>
+        <v>171.9938930677381</v>
       </c>
       <c r="X28">
-        <v>263.9907370700003</v>
+        <v>263.9907370748306</v>
       </c>
       <c r="Y28">
-        <v>467.9837446400006</v>
+        <v>467.9837446692391</v>
       </c>
       <c r="AB28">
         <v>21</v>
@@ -3673,19 +3673,19 @@
         <v>17</v>
       </c>
       <c r="AD28">
-        <v>31.19883402599998</v>
+        <v>31.19883401447305</v>
       </c>
       <c r="AE28">
-        <v>43.99822682000013</v>
+        <v>43.99822681929481</v>
       </c>
       <c r="AF28">
-        <v>94.99624575000009</v>
+        <v>94.99624575129565</v>
       </c>
       <c r="AG28">
-        <v>163.9933489699997</v>
+        <v>163.9933489420655</v>
       </c>
       <c r="AH28">
-        <v>335.9865549400001</v>
+        <v>335.9865548823918</v>
       </c>
       <c r="AK28">
         <v>21</v>
@@ -3694,19 +3694,19 @@
         <v>11</v>
       </c>
       <c r="AM28">
-        <v>106.7967655379944</v>
+        <v>106.7967654314707</v>
       </c>
       <c r="AN28">
-        <v>107.9967685299998</v>
+        <v>107.9967684258299</v>
       </c>
       <c r="AO28">
-        <v>422.9871463499949</v>
+        <v>422.987145931831</v>
       </c>
       <c r="AP28">
-        <v>782.9762062899972</v>
+        <v>782.9762055148894</v>
       </c>
       <c r="AQ28">
-        <v>1700.948260839996</v>
+        <v>1700.948259140256</v>
       </c>
       <c r="AT28">
         <v>21</v>
@@ -3715,19 +3715,19 @@
         <v>12</v>
       </c>
       <c r="AV28">
-        <v>38.99859150599696</v>
+        <v>38.99859159319567</v>
       </c>
       <c r="AW28">
-        <v>33.99893219000114</v>
+        <v>33.99893216317469</v>
       </c>
       <c r="AX28">
-        <v>255.9909572600009</v>
+        <v>255.9909571399712</v>
       </c>
       <c r="AY28">
-        <v>564.9787291699977</v>
+        <v>564.9787288731604</v>
       </c>
       <c r="AZ28">
-        <v>1162.957121890004</v>
+        <v>1162.95712149208</v>
       </c>
     </row>
     <row r="29" spans="1:52">
@@ -3738,19 +3738,19 @@
         <v>14</v>
       </c>
       <c r="C29">
-        <v>-49.2008094060011</v>
+        <v>-49.20080948742634</v>
       </c>
       <c r="D29">
-        <v>21.00006619000033</v>
+        <v>21.00006618277712</v>
       </c>
       <c r="E29">
-        <v>47.00031197999988</v>
+        <v>47.00031198218494</v>
       </c>
       <c r="F29">
-        <v>75.00047967999944</v>
+        <v>75.00047966152306</v>
       </c>
       <c r="G29">
-        <v>173.0015102899979</v>
+        <v>173.0015102989496</v>
       </c>
       <c r="J29">
         <v>26</v>
@@ -3759,19 +3759,19 @@
         <v>15</v>
       </c>
       <c r="L29">
-        <v>-64.80109621799784</v>
+        <v>-64.80109622727468</v>
       </c>
       <c r="M29">
-        <v>197.0024408900026</v>
+        <v>197.0024409942416</v>
       </c>
       <c r="N29">
-        <v>390.004718890008</v>
+        <v>390.0047191009307</v>
       </c>
       <c r="O29">
-        <v>597.007604710001</v>
+        <v>597.0076050093521</v>
       </c>
       <c r="P29">
-        <v>1124.014030120004</v>
+        <v>1124.014030671697</v>
       </c>
       <c r="S29">
         <v>26</v>
@@ -3780,19 +3780,19 @@
         <v>16</v>
       </c>
       <c r="U29">
-        <v>93.6013161660012</v>
+        <v>93.60131625033864</v>
       </c>
       <c r="V29">
-        <v>300.0045445199958</v>
+        <v>300.0045446867244</v>
       </c>
       <c r="W29">
-        <v>571.0089521199989</v>
+        <v>571.0089524530267</v>
       </c>
       <c r="X29">
-        <v>882.0134005200016</v>
+        <v>882.0134010708662</v>
       </c>
       <c r="Y29">
-        <v>1568.023419809993</v>
+        <v>1568.023420855212</v>
       </c>
       <c r="AB29">
         <v>26</v>
@@ -3801,19 +3801,19 @@
         <v>17</v>
       </c>
       <c r="AD29">
-        <v>82.2015798600014</v>
+        <v>82.20157986969934</v>
       </c>
       <c r="AE29">
-        <v>118.0026028900011</v>
+        <v>118.0026029180317</v>
       </c>
       <c r="AF29">
-        <v>269.0055319700014</v>
+        <v>269.0055320125848</v>
       </c>
       <c r="AG29">
-        <v>459.0089551299998</v>
+        <v>459.0089552302552</v>
       </c>
       <c r="AH29">
-        <v>893.0181951899995</v>
+        <v>893.0181953237643</v>
       </c>
       <c r="AK29">
         <v>26</v>
@@ -3822,19 +3822,19 @@
         <v>11</v>
       </c>
       <c r="AM29">
-        <v>232.803665352003</v>
+        <v>232.8036653841045</v>
       </c>
       <c r="AN29">
-        <v>239.003727380019</v>
+        <v>239.0037274195638</v>
       </c>
       <c r="AO29">
-        <v>927.0145517999918</v>
+        <v>927.014551958804</v>
       </c>
       <c r="AP29">
-        <v>1718.027039700028</v>
+        <v>1718.027039983564</v>
       </c>
       <c r="AQ29">
-        <v>3728.058751019999</v>
+        <v>3728.058751626239</v>
       </c>
       <c r="AT29">
         <v>26</v>
@@ -3843,19 +3843,19 @@
         <v>12</v>
       </c>
       <c r="AV29">
-        <v>199.8022485540205</v>
+        <v>199.802248579741</v>
       </c>
       <c r="AW29">
-        <v>152.0026807399917</v>
+        <v>152.0026810953786</v>
       </c>
       <c r="AX29">
-        <v>863.0148062399821</v>
+        <v>863.0148070453215</v>
       </c>
       <c r="AY29">
-        <v>1809.027663689987</v>
+        <v>1809.027665223359</v>
       </c>
       <c r="AZ29">
-        <v>3497.058540380007</v>
+        <v>3497.05854304276</v>
       </c>
     </row>
     <row r="30" spans="1:52">
@@ -3866,19 +3866,19 @@
         <v>14</v>
       </c>
       <c r="C30">
-        <v>-211.2005432340011</v>
+        <v>-211.2005431744601</v>
       </c>
       <c r="D30">
-        <v>40.99990902999889</v>
+        <v>40.99990903539219</v>
       </c>
       <c r="E30">
-        <v>106.999826549998</v>
+        <v>106.9998265270278</v>
       </c>
       <c r="F30">
-        <v>133.9998179899958</v>
+        <v>133.9998179285758</v>
       </c>
       <c r="G30">
-        <v>312.9997273599965</v>
+        <v>312.9997271767388</v>
       </c>
       <c r="J30">
         <v>24</v>
@@ -3887,19 +3887,19 @@
         <v>15</v>
       </c>
       <c r="L30">
-        <v>-49.79946939599904</v>
+        <v>-49.79946936496708</v>
       </c>
       <c r="M30">
-        <v>523.0002065400004</v>
+        <v>523.0002063326756</v>
       </c>
       <c r="N30">
-        <v>1006.000439349991</v>
+        <v>1006.000438955598</v>
       </c>
       <c r="O30">
-        <v>1568.000101109999</v>
+        <v>1568.000100502024</v>
       </c>
       <c r="P30">
-        <v>2752.000543740003</v>
+        <v>2752.00054265642</v>
       </c>
       <c r="S30">
         <v>24</v>
@@ -3908,19 +3908,19 @@
         <v>16</v>
       </c>
       <c r="U30">
-        <v>250.2001406099989</v>
+        <v>250.2001405275441</v>
       </c>
       <c r="V30">
-        <v>590.9991120100021</v>
+        <v>590.9991117551617</v>
       </c>
       <c r="W30">
-        <v>1156.998141529999</v>
+        <v>1156.998141026717</v>
       </c>
       <c r="X30">
-        <v>1794.997457689999</v>
+        <v>1794.997456945857</v>
       </c>
       <c r="Y30">
-        <v>3218.995827599989</v>
+        <v>3218.995826319424</v>
       </c>
       <c r="AB30">
         <v>24</v>
@@ -3929,19 +3929,19 @@
         <v>17</v>
       </c>
       <c r="AD30">
-        <v>131.9997177719988</v>
+        <v>131.9997177304767</v>
       </c>
       <c r="AE30">
-        <v>163.9992739900008</v>
+        <v>163.9992738857527</v>
       </c>
       <c r="AF30">
-        <v>361.9983912400012</v>
+        <v>361.9983910445044</v>
       </c>
       <c r="AG30">
-        <v>595.9980660099991</v>
+        <v>595.9980657110009</v>
       </c>
       <c r="AH30">
-        <v>1147.996008909995</v>
+        <v>1147.996008411368</v>
       </c>
       <c r="AK30">
         <v>24</v>
@@ -3950,19 +3950,19 @@
         <v>11</v>
       </c>
       <c r="AM30">
-        <v>532.7997976560291</v>
+        <v>532.7997974462633</v>
       </c>
       <c r="AN30">
-        <v>548.9997111099947</v>
+        <v>548.9997108932439</v>
       </c>
       <c r="AO30">
-        <v>2137.999217500008</v>
+        <v>2137.999216645519</v>
       </c>
       <c r="AP30">
-        <v>3962.998419559997</v>
+        <v>3962.998417995026</v>
       </c>
       <c r="AQ30">
-        <v>8594.996602399988</v>
+        <v>8594.996598993544</v>
       </c>
       <c r="AT30">
         <v>24</v>
@@ -3971,19 +3971,19 @@
         <v>12</v>
       </c>
       <c r="AV30">
-        <v>425.9996662079938</v>
+        <v>425.999666077274</v>
       </c>
       <c r="AW30">
-        <v>555.9988880999881</v>
+        <v>555.9988876271382</v>
       </c>
       <c r="AX30">
-        <v>2023.99581514996</v>
+        <v>2023.995813897156</v>
       </c>
       <c r="AY30">
-        <v>3829.997724460001</v>
+        <v>3829.997722388056</v>
       </c>
       <c r="AZ30">
-        <v>7418.992926900013</v>
+        <v>7418.992923493774</v>
       </c>
     </row>
     <row r="31" spans="1:52">
@@ -3994,19 +3994,19 @@
         <v>14</v>
       </c>
       <c r="C31">
-        <v>-394.1993695440033</v>
+        <v>-394.1993695519632</v>
       </c>
       <c r="D31">
-        <v>70.99995262999801</v>
+        <v>70.9999526363099</v>
       </c>
       <c r="E31">
-        <v>179.999802620001</v>
+        <v>179.9998026582798</v>
       </c>
       <c r="F31">
-        <v>181.9998235499988</v>
+        <v>181.9998236444626</v>
       </c>
       <c r="G31">
-        <v>429.9995466599976</v>
+        <v>429.9995468887901</v>
       </c>
       <c r="J31">
         <v>23</v>
@@ -4015,19 +4015,19 @@
         <v>15</v>
       </c>
       <c r="L31">
-        <v>52.7997821819954</v>
+        <v>52.79978219583427</v>
       </c>
       <c r="M31">
-        <v>673.9989602600035</v>
+        <v>673.9989604047005</v>
       </c>
       <c r="N31">
-        <v>1307.998046930006</v>
+        <v>1307.998047206704</v>
       </c>
       <c r="O31">
-        <v>2004.997012970001</v>
+        <v>2004.997013451284</v>
       </c>
       <c r="P31">
-        <v>3537.994837099992</v>
+        <v>3537.994837935606</v>
       </c>
       <c r="S31">
         <v>23</v>
@@ -4036,19 +4036,19 @@
         <v>16</v>
       </c>
       <c r="U31">
-        <v>338.999538905995</v>
+        <v>338.9995388956668</v>
       </c>
       <c r="V31">
-        <v>628.9992921099984</v>
+        <v>628.9992921226149</v>
       </c>
       <c r="W31">
-        <v>1226.998617369991</v>
+        <v>1226.99861742089</v>
       </c>
       <c r="X31">
-        <v>1948.997784699997</v>
+        <v>1948.997784740684</v>
       </c>
       <c r="Y31">
-        <v>3570.995870770003</v>
+        <v>3570.995870820338</v>
       </c>
       <c r="AB31">
         <v>23</v>
@@ -4057,19 +4057,19 @@
         <v>17</v>
       </c>
       <c r="AD31">
-        <v>163.1998272539995</v>
+        <v>163.1998272612745</v>
       </c>
       <c r="AE31">
-        <v>164.9998553400001</v>
+        <v>164.9998553643882</v>
       </c>
       <c r="AF31">
-        <v>341.9997048800005</v>
+        <v>341.9997049030735</v>
       </c>
       <c r="AG31">
-        <v>620.9994121499967</v>
+        <v>620.9994121313503</v>
       </c>
       <c r="AH31">
-        <v>1197.998782200004</v>
+        <v>1197.998782146</v>
       </c>
       <c r="AK31">
         <v>23</v>
@@ -4078,19 +4078,19 @@
         <v>11</v>
       </c>
       <c r="AM31">
-        <v>560.399688414007</v>
+        <v>560.3996882710198</v>
       </c>
       <c r="AN31">
-        <v>577.9997067899822</v>
+        <v>577.9997066454671</v>
       </c>
       <c r="AO31">
-        <v>2250.998765399971</v>
+        <v>2250.998764798584</v>
       </c>
       <c r="AP31">
-        <v>4168.997728969989</v>
+        <v>4168.997727865819</v>
       </c>
       <c r="AQ31">
-        <v>9045.995076890002</v>
+        <v>9045.995074490318</v>
       </c>
       <c r="AT31">
         <v>23</v>
@@ -4099,19 +4099,19 @@
         <v>12</v>
       </c>
       <c r="AV31">
-        <v>589.7993358119857</v>
+        <v>589.7993357993691</v>
       </c>
       <c r="AW31">
-        <v>481.9994443900068</v>
+        <v>481.9994446742057</v>
       </c>
       <c r="AX31">
-        <v>1872.997766360015</v>
+        <v>1872.997766750952</v>
       </c>
       <c r="AY31">
-        <v>4415.994657200004</v>
+        <v>4415.994657448726</v>
       </c>
       <c r="AZ31">
-        <v>8791.98880952</v>
+        <v>8791.988809695948</v>
       </c>
     </row>
     <row r="32" spans="1:52">
@@ -4122,19 +4122,19 @@
         <v>14</v>
       </c>
       <c r="C32">
-        <v>-69.60001584000111</v>
+        <v>-69.60001558614022</v>
       </c>
       <c r="D32">
-        <v>13.99999504000016</v>
+        <v>13.9999949770563</v>
       </c>
       <c r="E32">
-        <v>34.9999933199997</v>
+        <v>34.99999318854861</v>
       </c>
       <c r="F32">
-        <v>38.99999663000017</v>
+        <v>38.99999642818466</v>
       </c>
       <c r="G32">
-        <v>93.9999946500002</v>
+        <v>93.99999415179492</v>
       </c>
       <c r="J32">
         <v>25</v>
@@ -4143,19 +4143,19 @@
         <v>15</v>
       </c>
       <c r="L32">
-        <v>-15.0000103020011</v>
+        <v>-15.00001011831409</v>
       </c>
       <c r="M32">
-        <v>182.0000128700012</v>
+        <v>182.0000121127759</v>
       </c>
       <c r="N32">
-        <v>353.0000204300031</v>
+        <v>353.0000189169477</v>
       </c>
       <c r="O32">
-        <v>525.000040339999</v>
+        <v>525.0000380478614</v>
       </c>
       <c r="P32">
-        <v>917.0000842000009</v>
+        <v>917.0000800831676</v>
       </c>
       <c r="S32">
         <v>25</v>
@@ -4164,19 +4164,19 @@
         <v>16</v>
       </c>
       <c r="U32">
-        <v>82.80002890200012</v>
+        <v>82.80002852314738</v>
       </c>
       <c r="V32">
-        <v>194.0000500999995</v>
+        <v>194.0000490624507</v>
       </c>
       <c r="W32">
-        <v>377.0000958199998</v>
+        <v>377.0000938082485</v>
       </c>
       <c r="X32">
-        <v>584.0001515400008</v>
+        <v>584.00014846045</v>
       </c>
       <c r="Y32">
-        <v>1047.00029393</v>
+        <v>1047.000288395193</v>
       </c>
       <c r="AB32">
         <v>25</v>
@@ -4185,19 +4185,19 @@
         <v>17</v>
       </c>
       <c r="AD32">
-        <v>44.40000637200001</v>
+        <v>44.40000611084588</v>
       </c>
       <c r="AE32">
-        <v>55.99999884999988</v>
+        <v>55.99999850152108</v>
       </c>
       <c r="AF32">
-        <v>119.0000058399992</v>
+        <v>119.0000051080765</v>
       </c>
       <c r="AG32">
-        <v>211.0000061599994</v>
+        <v>211.0000049108635</v>
       </c>
       <c r="AH32">
-        <v>397.0000335999998</v>
+        <v>397.0000311649765</v>
       </c>
       <c r="AK32">
         <v>25</v>
@@ -4206,19 +4206,19 @@
         <v>11</v>
       </c>
       <c r="AM32">
-        <v>139.8000090960049</v>
+        <v>139.8000082357212</v>
       </c>
       <c r="AN32">
-        <v>142.0000119200049</v>
+        <v>142.0000110236142</v>
       </c>
       <c r="AO32">
-        <v>558.000036049998</v>
+        <v>558.0000325787005</v>
       </c>
       <c r="AP32">
-        <v>1034.000069529997</v>
+        <v>1034.000063085077</v>
       </c>
       <c r="AQ32">
-        <v>2244.000147989998</v>
+        <v>2244.000134008628</v>
       </c>
       <c r="AT32">
         <v>25</v>
@@ -4227,19 +4227,19 @@
         <v>12</v>
       </c>
       <c r="AV32">
-        <v>129.0000516420041</v>
+        <v>129.0000509986457</v>
       </c>
       <c r="AW32">
-        <v>188.9999717699975</v>
+        <v>188.9999709729491</v>
       </c>
       <c r="AX32">
-        <v>606.0001043099946</v>
+        <v>606.000101325455</v>
       </c>
       <c r="AY32">
-        <v>1238.000253210001</v>
+        <v>1238.000247139658</v>
       </c>
       <c r="AZ32">
-        <v>2332.000643489999</v>
+        <v>2332.000631624429</v>
       </c>
     </row>
     <row r="33" spans="1:52">
